--- a/data/REVISITAS_CENSO.xlsx
+++ b/data/REVISITAS_CENSO.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jp\Desktop\app_mobile_deep\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://deepessoas788-my.sharepoint.com/personal/joao_chaves_deepessoas_com_br/Documents/Área de Trabalho/app_mobile_deep/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590E7B65-DCE0-4A7F-8B69-5A1A8492D913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{3BEB9D3E-A7D7-4B87-B00C-B15F8E943B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC24FBC-2C0C-47F8-89E9-579096710AA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A41B31B-8B79-4EED-BC17-CE6031B2D227}"/>
+    <workbookView xWindow="20370" yWindow="-3390" windowWidth="29040" windowHeight="16440" xr2:uid="{9A41B31B-8B79-4EED-BC17-CE6031B2D227}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2626" uniqueCount="364">
   <si>
     <t>Link Backoffice</t>
   </si>
@@ -1075,13 +1075,73 @@
   </si>
   <si>
     <t>TESTE2_0009</t>
+  </si>
+  <si>
+    <t>TESTE 4</t>
+  </si>
+  <si>
+    <t>TESTE3_0001</t>
+  </si>
+  <si>
+    <t>TESTE3_0002</t>
+  </si>
+  <si>
+    <t>TESTE3_0003</t>
+  </si>
+  <si>
+    <t>TESTE3_0004</t>
+  </si>
+  <si>
+    <t>TESTE3_0005</t>
+  </si>
+  <si>
+    <t>TESTE3_0006</t>
+  </si>
+  <si>
+    <t>TESTE3_0007</t>
+  </si>
+  <si>
+    <t>TESTE3_0008</t>
+  </si>
+  <si>
+    <t>TESTE3_0009</t>
+  </si>
+  <si>
+    <t>TESTE 5(FINAL)</t>
+  </si>
+  <si>
+    <t>TESTE5_0001</t>
+  </si>
+  <si>
+    <t>TESTE5_0002</t>
+  </si>
+  <si>
+    <t>TESTE5_0003</t>
+  </si>
+  <si>
+    <t>TESTE5_0004</t>
+  </si>
+  <si>
+    <t>TESTE5_0005</t>
+  </si>
+  <si>
+    <t>TESTE5_0006</t>
+  </si>
+  <si>
+    <t>TESTE5_0007</t>
+  </si>
+  <si>
+    <t>TESTE5_0008</t>
+  </si>
+  <si>
+    <t>TESTE5_0009</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1117,6 +1177,22 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1154,7 +1230,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyBorder="1" applyProtection="1"/>
@@ -1165,6 +1241,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1502,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F27454-5C61-4644-A3C0-03706563E42B}">
-  <dimension ref="A1:GO46"/>
+  <dimension ref="A1:GO71"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="104.5703125" bestFit="1" customWidth="1"/>
@@ -1692,7 +1771,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -11871,7 +11950,7 @@
       <c r="B34" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="8" t="s">
         <v>194</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -15749,6 +15828,5395 @@
         <v>203</v>
       </c>
     </row>
+    <row r="47" spans="1:197" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="G47" s="6">
+        <v>46148</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J47" s="6">
+        <v>-22.936218</v>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6">
+        <v>-45.932715000000002</v>
+      </c>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="T47" s="6"/>
+      <c r="U47" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="V47" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="W47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="X47" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="6">
+        <v>50</v>
+      </c>
+      <c r="AB47" s="6">
+        <v>-22.9362137</v>
+      </c>
+      <c r="AC47" s="6">
+        <v>-45.932694300000001</v>
+      </c>
+      <c r="AD47" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE47" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF47" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH47" s="6"/>
+      <c r="AI47" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ47" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AK47" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL47" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AM47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN47" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AO47" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP47" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="AQ47" s="6">
+        <v>-22.936224200000002</v>
+      </c>
+      <c r="AR47" s="6">
+        <v>-45.9326559</v>
+      </c>
+      <c r="AS47" s="6"/>
+      <c r="AT47" s="6"/>
+      <c r="AU47" s="6"/>
+      <c r="AV47" s="6"/>
+      <c r="AW47" s="6"/>
+      <c r="AX47" s="6"/>
+      <c r="AY47" s="6"/>
+      <c r="AZ47" s="6"/>
+      <c r="BA47" s="6"/>
+      <c r="BB47" s="6"/>
+      <c r="BC47" s="6"/>
+      <c r="BD47" s="6"/>
+      <c r="BE47" s="6"/>
+      <c r="BF47" s="6"/>
+      <c r="BG47" s="6"/>
+      <c r="BH47" s="6"/>
+      <c r="BI47" s="6"/>
+      <c r="BJ47" s="6"/>
+      <c r="BK47" s="6"/>
+      <c r="BL47" s="6"/>
+      <c r="BM47" s="6"/>
+      <c r="BN47" s="6"/>
+      <c r="BO47" s="6"/>
+      <c r="BP47" s="6"/>
+      <c r="BQ47" s="6"/>
+      <c r="BR47" s="6"/>
+      <c r="BS47" s="6"/>
+      <c r="BT47" s="6"/>
+      <c r="BU47" s="6"/>
+      <c r="BV47" s="6"/>
+      <c r="BW47" s="6"/>
+      <c r="BX47" s="6"/>
+      <c r="BY47" s="6"/>
+      <c r="BZ47" s="6"/>
+      <c r="CA47" s="6"/>
+      <c r="CB47" s="6"/>
+      <c r="CC47" s="6"/>
+      <c r="CD47" s="6"/>
+      <c r="CE47" s="6"/>
+      <c r="CF47" s="6"/>
+      <c r="CG47" s="6"/>
+      <c r="CH47" s="6"/>
+      <c r="CI47" s="6"/>
+      <c r="CJ47" s="6"/>
+      <c r="CK47" s="6"/>
+      <c r="CL47" s="6"/>
+      <c r="CM47" s="6"/>
+      <c r="CN47" s="6"/>
+      <c r="CO47" s="6"/>
+      <c r="CP47" s="6"/>
+      <c r="CQ47" s="6"/>
+      <c r="CR47" s="6"/>
+      <c r="CS47" s="6"/>
+      <c r="CT47" s="6"/>
+      <c r="CU47" s="6"/>
+      <c r="CV47" s="6"/>
+      <c r="CW47" s="6"/>
+      <c r="CX47" s="6"/>
+      <c r="CY47" s="6"/>
+      <c r="CZ47" s="6"/>
+      <c r="DA47" s="6"/>
+      <c r="DB47" s="6"/>
+      <c r="DC47" s="6"/>
+      <c r="DD47" s="6"/>
+      <c r="DE47" s="6"/>
+      <c r="DF47" s="6"/>
+      <c r="DG47" s="6"/>
+      <c r="DH47" s="6"/>
+      <c r="DI47" s="6"/>
+      <c r="DJ47" s="6"/>
+      <c r="DK47" s="6"/>
+      <c r="DL47" s="6"/>
+      <c r="DM47" s="6"/>
+      <c r="DN47" s="6"/>
+      <c r="DO47" s="6"/>
+      <c r="DP47" s="6"/>
+      <c r="DQ47" s="6"/>
+      <c r="DR47" s="6"/>
+      <c r="DS47" s="6"/>
+      <c r="DT47" s="6"/>
+      <c r="DU47" s="6"/>
+      <c r="DV47" s="6"/>
+      <c r="DW47" s="6"/>
+      <c r="DX47" s="6"/>
+      <c r="DY47" s="6"/>
+      <c r="DZ47" s="6"/>
+      <c r="EA47" s="6"/>
+      <c r="EB47" s="6"/>
+      <c r="EC47" s="6"/>
+      <c r="ED47" s="6"/>
+      <c r="EE47" s="6"/>
+      <c r="EF47" s="6"/>
+      <c r="EG47" s="6"/>
+      <c r="EH47" s="6"/>
+      <c r="EI47" s="6"/>
+      <c r="EJ47" s="6"/>
+      <c r="EK47" s="6"/>
+      <c r="EL47" s="6"/>
+      <c r="EM47" s="6"/>
+      <c r="EN47" s="6"/>
+      <c r="EO47" s="6"/>
+      <c r="EP47" s="6"/>
+      <c r="EQ47" s="6"/>
+      <c r="ER47" s="6"/>
+      <c r="ES47" s="6"/>
+      <c r="ET47" s="6"/>
+      <c r="EU47" s="6"/>
+      <c r="EV47" s="6"/>
+      <c r="EW47" s="6"/>
+      <c r="EX47" s="6"/>
+      <c r="EY47" s="6"/>
+      <c r="EZ47" s="6"/>
+      <c r="FA47" s="6"/>
+      <c r="FB47" s="6"/>
+      <c r="FC47" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD47" s="6"/>
+      <c r="FE47" s="6"/>
+      <c r="FF47" s="6"/>
+      <c r="FG47" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="FH47" s="6"/>
+      <c r="FI47" s="6"/>
+      <c r="FJ47" s="6"/>
+      <c r="FK47" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL47" s="6"/>
+      <c r="FM47" s="6"/>
+      <c r="FN47" s="6"/>
+      <c r="FO47" s="6"/>
+      <c r="FP47" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="FQ47" s="6"/>
+      <c r="FR47" s="6"/>
+      <c r="FS47" s="6">
+        <v>-22.9144504504739</v>
+      </c>
+      <c r="FT47" s="6">
+        <v>-45.953700003562098</v>
+      </c>
+      <c r="FU47" s="6"/>
+      <c r="FV47" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW47" s="6"/>
+      <c r="FX47" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY47" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="FZ47" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="GA47" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="GB47" s="6"/>
+      <c r="GC47" s="6"/>
+      <c r="GD47" s="6"/>
+      <c r="GE47" s="6"/>
+      <c r="GF47" s="6"/>
+      <c r="GG47" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="GH47" s="6"/>
+      <c r="GI47" s="6"/>
+      <c r="GJ47" s="6">
+        <v>1</v>
+      </c>
+      <c r="GK47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL47" s="6"/>
+      <c r="GM47" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN47" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO47" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1">
+        <v>46171</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J48" s="1">
+        <v>-22.910423999999999</v>
+      </c>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1">
+        <v>-46.000855999999999</v>
+      </c>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1">
+        <v>500</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>-22.910055100000001</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>-46.001041000000001</v>
+      </c>
+      <c r="AD48" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE48" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF48" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL48" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AM48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN48" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP48" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="AQ48" s="1">
+        <v>-22.9103049</v>
+      </c>
+      <c r="AR48" s="1">
+        <v>-46.000889899999997</v>
+      </c>
+      <c r="AS48" s="1"/>
+      <c r="AT48" s="1"/>
+      <c r="AU48" s="1"/>
+      <c r="AV48" s="1"/>
+      <c r="AW48" s="1"/>
+      <c r="AX48" s="1"/>
+      <c r="AY48" s="1"/>
+      <c r="AZ48" s="1"/>
+      <c r="BA48" s="1"/>
+      <c r="BB48" s="1"/>
+      <c r="BC48" s="1"/>
+      <c r="BD48" s="1"/>
+      <c r="BE48" s="1"/>
+      <c r="BF48" s="1"/>
+      <c r="BG48" s="1"/>
+      <c r="BH48" s="1"/>
+      <c r="BI48" s="1"/>
+      <c r="BJ48" s="1"/>
+      <c r="BK48" s="1"/>
+      <c r="BL48" s="1"/>
+      <c r="BM48" s="1"/>
+      <c r="BN48" s="1"/>
+      <c r="BO48" s="1"/>
+      <c r="BP48" s="1"/>
+      <c r="BQ48" s="1"/>
+      <c r="BR48" s="1"/>
+      <c r="BS48" s="1"/>
+      <c r="BT48" s="1"/>
+      <c r="BU48" s="1"/>
+      <c r="BV48" s="1"/>
+      <c r="BW48" s="1"/>
+      <c r="BX48" s="1"/>
+      <c r="BY48" s="1"/>
+      <c r="BZ48" s="1"/>
+      <c r="CA48" s="1"/>
+      <c r="CB48" s="1"/>
+      <c r="CC48" s="1"/>
+      <c r="CD48" s="1"/>
+      <c r="CE48" s="1"/>
+      <c r="CF48" s="1"/>
+      <c r="CG48" s="1"/>
+      <c r="CH48" s="1"/>
+      <c r="CI48" s="1"/>
+      <c r="CJ48" s="1"/>
+      <c r="CK48" s="1"/>
+      <c r="CL48" s="1"/>
+      <c r="CM48" s="1"/>
+      <c r="CN48" s="1"/>
+      <c r="CO48" s="1"/>
+      <c r="CP48" s="1"/>
+      <c r="CQ48" s="1"/>
+      <c r="CR48" s="1"/>
+      <c r="CS48" s="1"/>
+      <c r="CT48" s="1"/>
+      <c r="CU48" s="1"/>
+      <c r="CV48" s="1"/>
+      <c r="CW48" s="1"/>
+      <c r="CX48" s="1"/>
+      <c r="CY48" s="1"/>
+      <c r="CZ48" s="1"/>
+      <c r="DA48" s="1"/>
+      <c r="DB48" s="1"/>
+      <c r="DC48" s="1"/>
+      <c r="DD48" s="1"/>
+      <c r="DE48" s="1"/>
+      <c r="DF48" s="1"/>
+      <c r="DG48" s="1"/>
+      <c r="DH48" s="1"/>
+      <c r="DI48" s="1"/>
+      <c r="DJ48" s="1"/>
+      <c r="DK48" s="1"/>
+      <c r="DL48" s="1"/>
+      <c r="DM48" s="1"/>
+      <c r="DN48" s="1"/>
+      <c r="DO48" s="1"/>
+      <c r="DP48" s="1"/>
+      <c r="DQ48" s="1"/>
+      <c r="DR48" s="1"/>
+      <c r="DS48" s="1"/>
+      <c r="DT48" s="1"/>
+      <c r="DU48" s="1"/>
+      <c r="DV48" s="1"/>
+      <c r="DW48" s="1"/>
+      <c r="DX48" s="1"/>
+      <c r="DY48" s="1"/>
+      <c r="DZ48" s="1"/>
+      <c r="EA48" s="1"/>
+      <c r="EB48" s="1"/>
+      <c r="EC48" s="1"/>
+      <c r="ED48" s="1"/>
+      <c r="EE48" s="1"/>
+      <c r="EF48" s="1"/>
+      <c r="EG48" s="1"/>
+      <c r="EH48" s="1"/>
+      <c r="EI48" s="1"/>
+      <c r="EJ48" s="1"/>
+      <c r="EK48" s="1"/>
+      <c r="EL48" s="1"/>
+      <c r="EM48" s="1"/>
+      <c r="EN48" s="1"/>
+      <c r="EO48" s="1"/>
+      <c r="EP48" s="1"/>
+      <c r="EQ48" s="1"/>
+      <c r="ER48" s="1"/>
+      <c r="ES48" s="1"/>
+      <c r="ET48" s="1"/>
+      <c r="EU48" s="1"/>
+      <c r="EV48" s="1"/>
+      <c r="EW48" s="1"/>
+      <c r="EX48" s="1"/>
+      <c r="EY48" s="1"/>
+      <c r="EZ48" s="1"/>
+      <c r="FA48" s="1"/>
+      <c r="FB48" s="1"/>
+      <c r="FC48" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD48" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="FE48" s="1"/>
+      <c r="FF48" s="1"/>
+      <c r="FG48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="FH48" s="1"/>
+      <c r="FI48" s="1"/>
+      <c r="FJ48" s="1"/>
+      <c r="FK48" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL48" s="1"/>
+      <c r="FM48" s="1"/>
+      <c r="FN48" s="1"/>
+      <c r="FO48" s="1"/>
+      <c r="FP48" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="FQ48" s="1"/>
+      <c r="FR48" s="1"/>
+      <c r="FS48" s="1">
+        <v>-22.915160568548298</v>
+      </c>
+      <c r="FT48" s="1">
+        <v>-46.009712190787802</v>
+      </c>
+      <c r="FU48" s="1"/>
+      <c r="FV48" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW48" s="1"/>
+      <c r="FX48" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="FZ48" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="GA48" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="GB48" s="1"/>
+      <c r="GC48" s="1"/>
+      <c r="GD48" s="1"/>
+      <c r="GE48" s="1"/>
+      <c r="GF48" s="1"/>
+      <c r="GG48" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH48" s="1"/>
+      <c r="GI48" s="1"/>
+      <c r="GJ48" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL48" s="1"/>
+      <c r="GM48" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN48" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO48" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G49" s="1">
+        <v>46171</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-22.920950000000001</v>
+      </c>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1">
+        <v>-46.006014999999998</v>
+      </c>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X49" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1">
+        <v>50</v>
+      </c>
+      <c r="AB49" s="1">
+        <v>-22.921104100000001</v>
+      </c>
+      <c r="AC49" s="1">
+        <v>-46.006032400000002</v>
+      </c>
+      <c r="AD49" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE49" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF49" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH49" s="1"/>
+      <c r="AI49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ49" s="1"/>
+      <c r="AK49" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL49" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AM49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN49" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO49" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP49" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AQ49" s="1">
+        <v>-22.921065299999999</v>
+      </c>
+      <c r="AR49" s="1">
+        <v>-46.006052199999999</v>
+      </c>
+      <c r="AS49" s="1"/>
+      <c r="AT49" s="1"/>
+      <c r="AU49" s="1"/>
+      <c r="AV49" s="1"/>
+      <c r="AW49" s="1"/>
+      <c r="AX49" s="1"/>
+      <c r="AY49" s="1"/>
+      <c r="AZ49" s="1"/>
+      <c r="BA49" s="1"/>
+      <c r="BB49" s="1"/>
+      <c r="BC49" s="1"/>
+      <c r="BD49" s="1"/>
+      <c r="BE49" s="1"/>
+      <c r="BF49" s="1"/>
+      <c r="BG49" s="1"/>
+      <c r="BH49" s="1"/>
+      <c r="BI49" s="1"/>
+      <c r="BJ49" s="1"/>
+      <c r="BK49" s="1"/>
+      <c r="BL49" s="1"/>
+      <c r="BM49" s="1"/>
+      <c r="BN49" s="1"/>
+      <c r="BO49" s="1"/>
+      <c r="BP49" s="1"/>
+      <c r="BQ49" s="1"/>
+      <c r="BR49" s="1"/>
+      <c r="BS49" s="1"/>
+      <c r="BT49" s="1"/>
+      <c r="BU49" s="1"/>
+      <c r="BV49" s="1"/>
+      <c r="BW49" s="1"/>
+      <c r="BX49" s="1"/>
+      <c r="BY49" s="1"/>
+      <c r="BZ49" s="1"/>
+      <c r="CA49" s="1"/>
+      <c r="CB49" s="1"/>
+      <c r="CC49" s="1"/>
+      <c r="CD49" s="1"/>
+      <c r="CE49" s="1"/>
+      <c r="CF49" s="1"/>
+      <c r="CG49" s="1"/>
+      <c r="CH49" s="1"/>
+      <c r="CI49" s="1"/>
+      <c r="CJ49" s="1"/>
+      <c r="CK49" s="1"/>
+      <c r="CL49" s="1"/>
+      <c r="CM49" s="1"/>
+      <c r="CN49" s="1"/>
+      <c r="CO49" s="1"/>
+      <c r="CP49" s="1"/>
+      <c r="CQ49" s="1"/>
+      <c r="CR49" s="1"/>
+      <c r="CS49" s="1"/>
+      <c r="CT49" s="1"/>
+      <c r="CU49" s="1"/>
+      <c r="CV49" s="1"/>
+      <c r="CW49" s="1"/>
+      <c r="CX49" s="1"/>
+      <c r="CY49" s="1"/>
+      <c r="CZ49" s="1"/>
+      <c r="DA49" s="1"/>
+      <c r="DB49" s="1"/>
+      <c r="DC49" s="1"/>
+      <c r="DD49" s="1"/>
+      <c r="DE49" s="1"/>
+      <c r="DF49" s="1"/>
+      <c r="DG49" s="1"/>
+      <c r="DH49" s="1"/>
+      <c r="DI49" s="1"/>
+      <c r="DJ49" s="1"/>
+      <c r="DK49" s="1"/>
+      <c r="DL49" s="1"/>
+      <c r="DM49" s="1"/>
+      <c r="DN49" s="1"/>
+      <c r="DO49" s="1"/>
+      <c r="DP49" s="1"/>
+      <c r="DQ49" s="1"/>
+      <c r="DR49" s="1"/>
+      <c r="DS49" s="1"/>
+      <c r="DT49" s="1"/>
+      <c r="DU49" s="1"/>
+      <c r="DV49" s="1"/>
+      <c r="DW49" s="1"/>
+      <c r="DX49" s="1"/>
+      <c r="DY49" s="1"/>
+      <c r="DZ49" s="1"/>
+      <c r="EA49" s="1"/>
+      <c r="EB49" s="1"/>
+      <c r="EC49" s="1"/>
+      <c r="ED49" s="1"/>
+      <c r="EE49" s="1"/>
+      <c r="EF49" s="1"/>
+      <c r="EG49" s="1"/>
+      <c r="EH49" s="1"/>
+      <c r="EI49" s="1"/>
+      <c r="EJ49" s="1"/>
+      <c r="EK49" s="1"/>
+      <c r="EL49" s="1"/>
+      <c r="EM49" s="1"/>
+      <c r="EN49" s="1"/>
+      <c r="EO49" s="1"/>
+      <c r="EP49" s="1"/>
+      <c r="EQ49" s="1"/>
+      <c r="ER49" s="1"/>
+      <c r="ES49" s="1"/>
+      <c r="ET49" s="1"/>
+      <c r="EU49" s="1"/>
+      <c r="EV49" s="1"/>
+      <c r="EW49" s="1"/>
+      <c r="EX49" s="1"/>
+      <c r="EY49" s="1"/>
+      <c r="EZ49" s="1"/>
+      <c r="FA49" s="1"/>
+      <c r="FB49" s="1"/>
+      <c r="FC49" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD49" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="FE49" s="1"/>
+      <c r="FF49" s="1"/>
+      <c r="FG49" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="FH49" s="1"/>
+      <c r="FI49" s="1"/>
+      <c r="FJ49" s="1"/>
+      <c r="FK49" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL49" s="1"/>
+      <c r="FM49" s="1"/>
+      <c r="FN49" s="1"/>
+      <c r="FO49" s="1"/>
+      <c r="FP49" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="FQ49" s="1"/>
+      <c r="FR49" s="1"/>
+      <c r="FS49" s="1">
+        <v>-22.915160568548298</v>
+      </c>
+      <c r="FT49" s="1">
+        <v>-46.009712190787802</v>
+      </c>
+      <c r="FU49" s="1"/>
+      <c r="FV49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW49" s="1"/>
+      <c r="FX49" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY49" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="FZ49" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="GA49" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="GB49" s="1"/>
+      <c r="GC49" s="1"/>
+      <c r="GD49" s="1"/>
+      <c r="GE49" s="1"/>
+      <c r="GF49" s="1"/>
+      <c r="GG49" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH49" s="1"/>
+      <c r="GI49" s="1"/>
+      <c r="GJ49" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL49" s="1"/>
+      <c r="GM49" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN49" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO49" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G50" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-22.850884000000001</v>
+      </c>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1">
+        <v>-45.928733000000001</v>
+      </c>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X50" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>-22.850901400000001</v>
+      </c>
+      <c r="AC50" s="1">
+        <v>-45.928720599999998</v>
+      </c>
+      <c r="AD50" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF50" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL50" s="1"/>
+      <c r="AM50" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP50" s="1"/>
+      <c r="AQ50" s="1">
+        <v>-22.850910599999999</v>
+      </c>
+      <c r="AR50" s="1">
+        <v>-45.928714200000002</v>
+      </c>
+      <c r="AS50" s="1"/>
+      <c r="AT50" s="1"/>
+      <c r="AU50" s="1"/>
+      <c r="AV50" s="1"/>
+      <c r="AW50" s="1"/>
+      <c r="AX50" s="1"/>
+      <c r="AY50" s="1"/>
+      <c r="AZ50" s="1"/>
+      <c r="BA50" s="1"/>
+      <c r="BB50" s="1"/>
+      <c r="BC50" s="1"/>
+      <c r="BD50" s="1"/>
+      <c r="BE50" s="1"/>
+      <c r="BF50" s="1"/>
+      <c r="BG50" s="1"/>
+      <c r="BH50" s="1"/>
+      <c r="BI50" s="1"/>
+      <c r="BJ50" s="1"/>
+      <c r="BK50" s="1"/>
+      <c r="BL50" s="1"/>
+      <c r="BM50" s="1"/>
+      <c r="BN50" s="1"/>
+      <c r="BO50" s="1"/>
+      <c r="BP50" s="1"/>
+      <c r="BQ50" s="1"/>
+      <c r="BR50" s="1"/>
+      <c r="BS50" s="1"/>
+      <c r="BT50" s="1"/>
+      <c r="BU50" s="1"/>
+      <c r="BV50" s="1"/>
+      <c r="BW50" s="1"/>
+      <c r="BX50" s="1"/>
+      <c r="BY50" s="1"/>
+      <c r="BZ50" s="1"/>
+      <c r="CA50" s="1"/>
+      <c r="CB50" s="1"/>
+      <c r="CC50" s="1"/>
+      <c r="CD50" s="1"/>
+      <c r="CE50" s="1"/>
+      <c r="CF50" s="1"/>
+      <c r="CG50" s="1"/>
+      <c r="CH50" s="1"/>
+      <c r="CI50" s="1"/>
+      <c r="CJ50" s="1"/>
+      <c r="CK50" s="1"/>
+      <c r="CL50" s="1"/>
+      <c r="CM50" s="1"/>
+      <c r="CN50" s="1"/>
+      <c r="CO50" s="1"/>
+      <c r="CP50" s="1"/>
+      <c r="CQ50" s="1"/>
+      <c r="CR50" s="1"/>
+      <c r="CS50" s="1"/>
+      <c r="CT50" s="1"/>
+      <c r="CU50" s="1"/>
+      <c r="CV50" s="1"/>
+      <c r="CW50" s="1"/>
+      <c r="CX50" s="1"/>
+      <c r="CY50" s="1"/>
+      <c r="CZ50" s="1"/>
+      <c r="DA50" s="1"/>
+      <c r="DB50" s="1"/>
+      <c r="DC50" s="1"/>
+      <c r="DD50" s="1"/>
+      <c r="DE50" s="1"/>
+      <c r="DF50" s="1"/>
+      <c r="DG50" s="1"/>
+      <c r="DH50" s="1"/>
+      <c r="DI50" s="1"/>
+      <c r="DJ50" s="1"/>
+      <c r="DK50" s="1"/>
+      <c r="DL50" s="1"/>
+      <c r="DM50" s="1"/>
+      <c r="DN50" s="1"/>
+      <c r="DO50" s="1"/>
+      <c r="DP50" s="1"/>
+      <c r="DQ50" s="1"/>
+      <c r="DR50" s="1"/>
+      <c r="DS50" s="1"/>
+      <c r="DT50" s="1"/>
+      <c r="DU50" s="1"/>
+      <c r="DV50" s="1"/>
+      <c r="DW50" s="1"/>
+      <c r="DX50" s="1"/>
+      <c r="DY50" s="1"/>
+      <c r="DZ50" s="1"/>
+      <c r="EA50" s="1"/>
+      <c r="EB50" s="1"/>
+      <c r="EC50" s="1"/>
+      <c r="ED50" s="1"/>
+      <c r="EE50" s="1"/>
+      <c r="EF50" s="1"/>
+      <c r="EG50" s="1"/>
+      <c r="EH50" s="1"/>
+      <c r="EI50" s="1"/>
+      <c r="EJ50" s="1"/>
+      <c r="EK50" s="1"/>
+      <c r="EL50" s="1"/>
+      <c r="EM50" s="1"/>
+      <c r="EN50" s="1"/>
+      <c r="EO50" s="1"/>
+      <c r="EP50" s="1"/>
+      <c r="EQ50" s="1"/>
+      <c r="ER50" s="1"/>
+      <c r="ES50" s="1"/>
+      <c r="ET50" s="1"/>
+      <c r="EU50" s="1"/>
+      <c r="EV50" s="1"/>
+      <c r="EW50" s="1"/>
+      <c r="EX50" s="1"/>
+      <c r="EY50" s="1"/>
+      <c r="EZ50" s="1"/>
+      <c r="FA50" s="1"/>
+      <c r="FB50" s="1"/>
+      <c r="FC50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD50" s="1"/>
+      <c r="FE50" s="1"/>
+      <c r="FF50" s="1"/>
+      <c r="FG50" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="FH50" s="1"/>
+      <c r="FI50" s="1"/>
+      <c r="FJ50" s="1"/>
+      <c r="FK50" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL50" s="1"/>
+      <c r="FM50" s="1"/>
+      <c r="FN50" s="1"/>
+      <c r="FO50" s="1"/>
+      <c r="FP50" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="FQ50" s="1"/>
+      <c r="FR50" s="1"/>
+      <c r="FS50" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT50" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU50" s="1"/>
+      <c r="FV50" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW50" s="1"/>
+      <c r="FX50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY50" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ50" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="GA50" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="GB50" s="1"/>
+      <c r="GC50" s="1"/>
+      <c r="GD50" s="1"/>
+      <c r="GE50" s="1"/>
+      <c r="GF50" s="1"/>
+      <c r="GG50" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH50" s="1"/>
+      <c r="GI50" s="1"/>
+      <c r="GJ50" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL50" s="1"/>
+      <c r="GM50" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN50" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO50" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G51" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J51" s="1">
+        <v>-22.855927999999999</v>
+      </c>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1">
+        <v>-45.933276999999997</v>
+      </c>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1">
+        <v>100</v>
+      </c>
+      <c r="AB51" s="1">
+        <v>-22.8553633</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>-45.934085000000003</v>
+      </c>
+      <c r="AD51" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE51" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF51" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG51" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH51" s="1">
+        <v>2100</v>
+      </c>
+      <c r="AI51" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ51" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK51" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL51" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AM51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AO51" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP51" s="1"/>
+      <c r="AQ51" s="1"/>
+      <c r="AR51" s="1"/>
+      <c r="AS51" s="1"/>
+      <c r="AT51" s="1"/>
+      <c r="AU51" s="1"/>
+      <c r="AV51" s="1"/>
+      <c r="AW51" s="1"/>
+      <c r="AX51" s="1"/>
+      <c r="AY51" s="1"/>
+      <c r="AZ51" s="1"/>
+      <c r="BA51" s="1"/>
+      <c r="BB51" s="1"/>
+      <c r="BC51" s="1"/>
+      <c r="BD51" s="1"/>
+      <c r="BE51" s="1"/>
+      <c r="BF51" s="1"/>
+      <c r="BG51" s="1"/>
+      <c r="BH51" s="1"/>
+      <c r="BI51" s="1"/>
+      <c r="BJ51" s="1"/>
+      <c r="BK51" s="1"/>
+      <c r="BL51" s="1"/>
+      <c r="BM51" s="1"/>
+      <c r="BN51" s="1"/>
+      <c r="BO51" s="1"/>
+      <c r="BP51" s="1"/>
+      <c r="BQ51" s="1"/>
+      <c r="BR51" s="1"/>
+      <c r="BS51" s="1"/>
+      <c r="BT51" s="1"/>
+      <c r="BU51" s="1"/>
+      <c r="BV51" s="1"/>
+      <c r="BW51" s="1"/>
+      <c r="BX51" s="1"/>
+      <c r="BY51" s="1"/>
+      <c r="BZ51" s="1"/>
+      <c r="CA51" s="1"/>
+      <c r="CB51" s="1"/>
+      <c r="CC51" s="1"/>
+      <c r="CD51" s="1"/>
+      <c r="CE51" s="1"/>
+      <c r="CF51" s="1"/>
+      <c r="CG51" s="1"/>
+      <c r="CH51" s="1"/>
+      <c r="CI51" s="1"/>
+      <c r="CJ51" s="1"/>
+      <c r="CK51" s="1"/>
+      <c r="CL51" s="1"/>
+      <c r="CM51" s="1"/>
+      <c r="CN51" s="1"/>
+      <c r="CO51" s="1"/>
+      <c r="CP51" s="1"/>
+      <c r="CQ51" s="1"/>
+      <c r="CR51" s="1"/>
+      <c r="CS51" s="1"/>
+      <c r="CT51" s="1"/>
+      <c r="CU51" s="1"/>
+      <c r="CV51" s="1"/>
+      <c r="CW51" s="1"/>
+      <c r="CX51" s="1"/>
+      <c r="CY51" s="1"/>
+      <c r="CZ51" s="1"/>
+      <c r="DA51" s="1"/>
+      <c r="DB51" s="1"/>
+      <c r="DC51" s="1"/>
+      <c r="DD51" s="1"/>
+      <c r="DE51" s="1"/>
+      <c r="DF51" s="1"/>
+      <c r="DG51" s="1"/>
+      <c r="DH51" s="1"/>
+      <c r="DI51" s="1"/>
+      <c r="DJ51" s="1"/>
+      <c r="DK51" s="1"/>
+      <c r="DL51" s="1"/>
+      <c r="DM51" s="1"/>
+      <c r="DN51" s="1"/>
+      <c r="DO51" s="1"/>
+      <c r="DP51" s="1"/>
+      <c r="DQ51" s="1"/>
+      <c r="DR51" s="1"/>
+      <c r="DS51" s="1"/>
+      <c r="DT51" s="1"/>
+      <c r="DU51" s="1"/>
+      <c r="DV51" s="1"/>
+      <c r="DW51" s="1"/>
+      <c r="DX51" s="1"/>
+      <c r="DY51" s="1"/>
+      <c r="DZ51" s="1"/>
+      <c r="EA51" s="1"/>
+      <c r="EB51" s="1"/>
+      <c r="EC51" s="1"/>
+      <c r="ED51" s="1"/>
+      <c r="EE51" s="1"/>
+      <c r="EF51" s="1"/>
+      <c r="EG51" s="1"/>
+      <c r="EH51" s="1"/>
+      <c r="EI51" s="1"/>
+      <c r="EJ51" s="1"/>
+      <c r="EK51" s="1"/>
+      <c r="EL51" s="1"/>
+      <c r="EM51" s="1"/>
+      <c r="EN51" s="1"/>
+      <c r="EO51" s="1"/>
+      <c r="EP51" s="1"/>
+      <c r="EQ51" s="1"/>
+      <c r="ER51" s="1"/>
+      <c r="ES51" s="1"/>
+      <c r="ET51" s="1"/>
+      <c r="EU51" s="1"/>
+      <c r="EV51" s="1"/>
+      <c r="EW51" s="1"/>
+      <c r="EX51" s="1"/>
+      <c r="EY51" s="1"/>
+      <c r="EZ51" s="1"/>
+      <c r="FA51" s="1"/>
+      <c r="FB51" s="1"/>
+      <c r="FC51" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD51" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="FE51" s="1"/>
+      <c r="FF51" s="1"/>
+      <c r="FG51" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="FH51" s="1"/>
+      <c r="FI51" s="1"/>
+      <c r="FJ51" s="1"/>
+      <c r="FK51" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL51" s="1"/>
+      <c r="FM51" s="1"/>
+      <c r="FN51" s="1"/>
+      <c r="FO51" s="1"/>
+      <c r="FP51" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="FQ51" s="1"/>
+      <c r="FR51" s="1"/>
+      <c r="FS51" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT51" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU51" s="1"/>
+      <c r="FV51" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW51" s="1"/>
+      <c r="FX51" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY51" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ51" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="GA51" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="GB51" s="1"/>
+      <c r="GC51" s="1"/>
+      <c r="GD51" s="1"/>
+      <c r="GE51" s="1"/>
+      <c r="GF51" s="1"/>
+      <c r="GG51" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH51" s="1"/>
+      <c r="GI51" s="1"/>
+      <c r="GJ51" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL51" s="1"/>
+      <c r="GM51" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN51" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO51" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G52" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J52" s="1">
+        <v>-22.862606</v>
+      </c>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1">
+        <v>-45.931848000000002</v>
+      </c>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1">
+        <v>-22.862584399999999</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>-45.931886499999997</v>
+      </c>
+      <c r="AD52" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE52" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF52" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG52" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH52" s="1">
+        <v>5600</v>
+      </c>
+      <c r="AI52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ52" s="1"/>
+      <c r="AK52" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL52" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="AM52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO52" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP52" s="1"/>
+      <c r="AQ52" s="1"/>
+      <c r="AR52" s="1"/>
+      <c r="AS52" s="1"/>
+      <c r="AT52" s="1"/>
+      <c r="AU52" s="1"/>
+      <c r="AV52" s="1"/>
+      <c r="AW52" s="1"/>
+      <c r="AX52" s="1"/>
+      <c r="AY52" s="1"/>
+      <c r="AZ52" s="1"/>
+      <c r="BA52" s="1"/>
+      <c r="BB52" s="1"/>
+      <c r="BC52" s="1"/>
+      <c r="BD52" s="1"/>
+      <c r="BE52" s="1"/>
+      <c r="BF52" s="1"/>
+      <c r="BG52" s="1"/>
+      <c r="BH52" s="1"/>
+      <c r="BI52" s="1"/>
+      <c r="BJ52" s="1"/>
+      <c r="BK52" s="1"/>
+      <c r="BL52" s="1"/>
+      <c r="BM52" s="1"/>
+      <c r="BN52" s="1"/>
+      <c r="BO52" s="1"/>
+      <c r="BP52" s="1"/>
+      <c r="BQ52" s="1"/>
+      <c r="BR52" s="1"/>
+      <c r="BS52" s="1"/>
+      <c r="BT52" s="1"/>
+      <c r="BU52" s="1"/>
+      <c r="BV52" s="1"/>
+      <c r="BW52" s="1"/>
+      <c r="BX52" s="1"/>
+      <c r="BY52" s="1"/>
+      <c r="BZ52" s="1"/>
+      <c r="CA52" s="1"/>
+      <c r="CB52" s="1"/>
+      <c r="CC52" s="1"/>
+      <c r="CD52" s="1"/>
+      <c r="CE52" s="1"/>
+      <c r="CF52" s="1"/>
+      <c r="CG52" s="1"/>
+      <c r="CH52" s="1"/>
+      <c r="CI52" s="1"/>
+      <c r="CJ52" s="1"/>
+      <c r="CK52" s="1"/>
+      <c r="CL52" s="1"/>
+      <c r="CM52" s="1"/>
+      <c r="CN52" s="1"/>
+      <c r="CO52" s="1"/>
+      <c r="CP52" s="1"/>
+      <c r="CQ52" s="1"/>
+      <c r="CR52" s="1"/>
+      <c r="CS52" s="1"/>
+      <c r="CT52" s="1"/>
+      <c r="CU52" s="1"/>
+      <c r="CV52" s="1"/>
+      <c r="CW52" s="1"/>
+      <c r="CX52" s="1"/>
+      <c r="CY52" s="1"/>
+      <c r="CZ52" s="1"/>
+      <c r="DA52" s="1"/>
+      <c r="DB52" s="1"/>
+      <c r="DC52" s="1"/>
+      <c r="DD52" s="1"/>
+      <c r="DE52" s="1"/>
+      <c r="DF52" s="1"/>
+      <c r="DG52" s="1"/>
+      <c r="DH52" s="1"/>
+      <c r="DI52" s="1"/>
+      <c r="DJ52" s="1"/>
+      <c r="DK52" s="1"/>
+      <c r="DL52" s="1"/>
+      <c r="DM52" s="1"/>
+      <c r="DN52" s="1"/>
+      <c r="DO52" s="1"/>
+      <c r="DP52" s="1"/>
+      <c r="DQ52" s="1"/>
+      <c r="DR52" s="1"/>
+      <c r="DS52" s="1"/>
+      <c r="DT52" s="1"/>
+      <c r="DU52" s="1"/>
+      <c r="DV52" s="1"/>
+      <c r="DW52" s="1"/>
+      <c r="DX52" s="1"/>
+      <c r="DY52" s="1"/>
+      <c r="DZ52" s="1"/>
+      <c r="EA52" s="1"/>
+      <c r="EB52" s="1"/>
+      <c r="EC52" s="1"/>
+      <c r="ED52" s="1"/>
+      <c r="EE52" s="1"/>
+      <c r="EF52" s="1"/>
+      <c r="EG52" s="1"/>
+      <c r="EH52" s="1"/>
+      <c r="EI52" s="1"/>
+      <c r="EJ52" s="1"/>
+      <c r="EK52" s="1"/>
+      <c r="EL52" s="1"/>
+      <c r="EM52" s="1"/>
+      <c r="EN52" s="1"/>
+      <c r="EO52" s="1"/>
+      <c r="EP52" s="1"/>
+      <c r="EQ52" s="1"/>
+      <c r="ER52" s="1"/>
+      <c r="ES52" s="1"/>
+      <c r="ET52" s="1"/>
+      <c r="EU52" s="1"/>
+      <c r="EV52" s="1"/>
+      <c r="EW52" s="1"/>
+      <c r="EX52" s="1"/>
+      <c r="EY52" s="1"/>
+      <c r="EZ52" s="1"/>
+      <c r="FA52" s="1"/>
+      <c r="FB52" s="1"/>
+      <c r="FC52" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD52" s="1"/>
+      <c r="FE52" s="1"/>
+      <c r="FF52" s="1"/>
+      <c r="FG52" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="FH52" s="1"/>
+      <c r="FI52" s="1"/>
+      <c r="FJ52" s="1"/>
+      <c r="FK52" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL52" s="1"/>
+      <c r="FM52" s="1"/>
+      <c r="FN52" s="1"/>
+      <c r="FO52" s="1"/>
+      <c r="FP52" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="FQ52" s="1"/>
+      <c r="FR52" s="1"/>
+      <c r="FS52" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT52" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU52" s="1"/>
+      <c r="FV52" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW52" s="1"/>
+      <c r="FX52" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY52" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ52" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="GA52" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="GB52" s="1"/>
+      <c r="GC52" s="1"/>
+      <c r="GD52" s="1"/>
+      <c r="GE52" s="1"/>
+      <c r="GF52" s="1"/>
+      <c r="GG52" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH52" s="1"/>
+      <c r="GI52" s="1"/>
+      <c r="GJ52" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL52" s="1"/>
+      <c r="GM52" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN52" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO52" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G53" s="1">
+        <v>46134</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J53" s="1">
+        <v>-22.925559</v>
+      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1">
+        <v>-45.983710000000002</v>
+      </c>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1">
+        <v>-22.9255532</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>-45.983625699999997</v>
+      </c>
+      <c r="AD53" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE53" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF53" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AG53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ53" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AK53" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL53" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AM53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO53" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP53" s="1"/>
+      <c r="AQ53" s="1"/>
+      <c r="AR53" s="1"/>
+      <c r="AS53" s="1"/>
+      <c r="AT53" s="1"/>
+      <c r="AU53" s="1"/>
+      <c r="AV53" s="1"/>
+      <c r="AW53" s="1"/>
+      <c r="AX53" s="1"/>
+      <c r="AY53" s="1"/>
+      <c r="AZ53" s="1"/>
+      <c r="BA53" s="1"/>
+      <c r="BB53" s="1"/>
+      <c r="BC53" s="1"/>
+      <c r="BD53" s="1"/>
+      <c r="BE53" s="1"/>
+      <c r="BF53" s="1"/>
+      <c r="BG53" s="1"/>
+      <c r="BH53" s="1"/>
+      <c r="BI53" s="1"/>
+      <c r="BJ53" s="1"/>
+      <c r="BK53" s="1"/>
+      <c r="BL53" s="1"/>
+      <c r="BM53" s="1"/>
+      <c r="BN53" s="1"/>
+      <c r="BO53" s="1"/>
+      <c r="BP53" s="1"/>
+      <c r="BQ53" s="1"/>
+      <c r="BR53" s="1"/>
+      <c r="BS53" s="1"/>
+      <c r="BT53" s="1"/>
+      <c r="BU53" s="1"/>
+      <c r="BV53" s="1"/>
+      <c r="BW53" s="1"/>
+      <c r="BX53" s="1"/>
+      <c r="BY53" s="1"/>
+      <c r="BZ53" s="1"/>
+      <c r="CA53" s="1"/>
+      <c r="CB53" s="1"/>
+      <c r="CC53" s="1"/>
+      <c r="CD53" s="1"/>
+      <c r="CE53" s="1"/>
+      <c r="CF53" s="1"/>
+      <c r="CG53" s="1"/>
+      <c r="CH53" s="1"/>
+      <c r="CI53" s="1"/>
+      <c r="CJ53" s="1"/>
+      <c r="CK53" s="1"/>
+      <c r="CL53" s="1"/>
+      <c r="CM53" s="1"/>
+      <c r="CN53" s="1"/>
+      <c r="CO53" s="1"/>
+      <c r="CP53" s="1"/>
+      <c r="CQ53" s="1"/>
+      <c r="CR53" s="1"/>
+      <c r="CS53" s="1"/>
+      <c r="CT53" s="1"/>
+      <c r="CU53" s="1"/>
+      <c r="CV53" s="1"/>
+      <c r="CW53" s="1"/>
+      <c r="CX53" s="1"/>
+      <c r="CY53" s="1"/>
+      <c r="CZ53" s="1"/>
+      <c r="DA53" s="1"/>
+      <c r="DB53" s="1"/>
+      <c r="DC53" s="1"/>
+      <c r="DD53" s="1"/>
+      <c r="DE53" s="1"/>
+      <c r="DF53" s="1"/>
+      <c r="DG53" s="1"/>
+      <c r="DH53" s="1"/>
+      <c r="DI53" s="1"/>
+      <c r="DJ53" s="1"/>
+      <c r="DK53" s="1"/>
+      <c r="DL53" s="1"/>
+      <c r="DM53" s="1"/>
+      <c r="DN53" s="1"/>
+      <c r="DO53" s="1"/>
+      <c r="DP53" s="1"/>
+      <c r="DQ53" s="1"/>
+      <c r="DR53" s="1"/>
+      <c r="DS53" s="1"/>
+      <c r="DT53" s="1"/>
+      <c r="DU53" s="1"/>
+      <c r="DV53" s="1"/>
+      <c r="DW53" s="1"/>
+      <c r="DX53" s="1"/>
+      <c r="DY53" s="1"/>
+      <c r="DZ53" s="1"/>
+      <c r="EA53" s="1"/>
+      <c r="EB53" s="1"/>
+      <c r="EC53" s="1"/>
+      <c r="ED53" s="1"/>
+      <c r="EE53" s="1"/>
+      <c r="EF53" s="1"/>
+      <c r="EG53" s="1"/>
+      <c r="EH53" s="1"/>
+      <c r="EI53" s="1"/>
+      <c r="EJ53" s="1"/>
+      <c r="EK53" s="1"/>
+      <c r="EL53" s="1"/>
+      <c r="EM53" s="1"/>
+      <c r="EN53" s="1"/>
+      <c r="EO53" s="1"/>
+      <c r="EP53" s="1"/>
+      <c r="EQ53" s="1"/>
+      <c r="ER53" s="1"/>
+      <c r="ES53" s="1"/>
+      <c r="ET53" s="1"/>
+      <c r="EU53" s="1"/>
+      <c r="EV53" s="1"/>
+      <c r="EW53" s="1"/>
+      <c r="EX53" s="1"/>
+      <c r="EY53" s="1"/>
+      <c r="EZ53" s="1"/>
+      <c r="FA53" s="1"/>
+      <c r="FB53" s="1"/>
+      <c r="FC53" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD53" s="1"/>
+      <c r="FE53" s="1"/>
+      <c r="FF53" s="1"/>
+      <c r="FG53" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="FH53" s="1"/>
+      <c r="FI53" s="1"/>
+      <c r="FJ53" s="1"/>
+      <c r="FK53" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL53" s="1"/>
+      <c r="FM53" s="1"/>
+      <c r="FN53" s="1"/>
+      <c r="FO53" s="1"/>
+      <c r="FP53" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="FQ53" s="1"/>
+      <c r="FR53" s="1"/>
+      <c r="FS53" s="1">
+        <v>-22.9295902170612</v>
+      </c>
+      <c r="FT53" s="1">
+        <v>-45.979329275508498</v>
+      </c>
+      <c r="FU53" s="1"/>
+      <c r="FV53" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW53" s="1"/>
+      <c r="FX53" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY53" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ53" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="GA53" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="GB53" s="1"/>
+      <c r="GC53" s="1"/>
+      <c r="GD53" s="1"/>
+      <c r="GE53" s="1"/>
+      <c r="GF53" s="1"/>
+      <c r="GG53" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="GH53" s="1"/>
+      <c r="GI53" s="1"/>
+      <c r="GJ53" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL53" s="1"/>
+      <c r="GM53" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN53" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO53" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G54" s="1">
+        <v>46129</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-22.923100000000002</v>
+      </c>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1">
+        <v>-45.976080000000003</v>
+      </c>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1">
+        <v>3000</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>-22.922883299999999</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>-45.976044999999999</v>
+      </c>
+      <c r="AD54" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE54" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF54" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AG54" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH54" s="1">
+        <v>2018</v>
+      </c>
+      <c r="AI54" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ54" s="1"/>
+      <c r="AK54" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL54" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AM54" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN54" s="1"/>
+      <c r="AO54" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP54" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AQ54" s="1"/>
+      <c r="AR54" s="1"/>
+      <c r="AS54" s="1"/>
+      <c r="AT54" s="1"/>
+      <c r="AU54" s="1"/>
+      <c r="AV54" s="1"/>
+      <c r="AW54" s="1"/>
+      <c r="AX54" s="1"/>
+      <c r="AY54" s="1"/>
+      <c r="AZ54" s="1"/>
+      <c r="BA54" s="1"/>
+      <c r="BB54" s="1"/>
+      <c r="BC54" s="1"/>
+      <c r="BD54" s="1"/>
+      <c r="BE54" s="1"/>
+      <c r="BF54" s="1"/>
+      <c r="BG54" s="1"/>
+      <c r="BH54" s="1"/>
+      <c r="BI54" s="1"/>
+      <c r="BJ54" s="1"/>
+      <c r="BK54" s="1"/>
+      <c r="BL54" s="1"/>
+      <c r="BM54" s="1"/>
+      <c r="BN54" s="1"/>
+      <c r="BO54" s="1"/>
+      <c r="BP54" s="1"/>
+      <c r="BQ54" s="1"/>
+      <c r="BR54" s="1"/>
+      <c r="BS54" s="1"/>
+      <c r="BT54" s="1"/>
+      <c r="BU54" s="1"/>
+      <c r="BV54" s="1"/>
+      <c r="BW54" s="1"/>
+      <c r="BX54" s="1"/>
+      <c r="BY54" s="1"/>
+      <c r="BZ54" s="1"/>
+      <c r="CA54" s="1"/>
+      <c r="CB54" s="1"/>
+      <c r="CC54" s="1"/>
+      <c r="CD54" s="1"/>
+      <c r="CE54" s="1"/>
+      <c r="CF54" s="1"/>
+      <c r="CG54" s="1"/>
+      <c r="CH54" s="1"/>
+      <c r="CI54" s="1"/>
+      <c r="CJ54" s="1"/>
+      <c r="CK54" s="1"/>
+      <c r="CL54" s="1"/>
+      <c r="CM54" s="1"/>
+      <c r="CN54" s="1"/>
+      <c r="CO54" s="1"/>
+      <c r="CP54" s="1"/>
+      <c r="CQ54" s="1"/>
+      <c r="CR54" s="1"/>
+      <c r="CS54" s="1"/>
+      <c r="CT54" s="1"/>
+      <c r="CU54" s="1"/>
+      <c r="CV54" s="1"/>
+      <c r="CW54" s="1"/>
+      <c r="CX54" s="1"/>
+      <c r="CY54" s="1"/>
+      <c r="CZ54" s="1"/>
+      <c r="DA54" s="1"/>
+      <c r="DB54" s="1"/>
+      <c r="DC54" s="1"/>
+      <c r="DD54" s="1"/>
+      <c r="DE54" s="1"/>
+      <c r="DF54" s="1"/>
+      <c r="DG54" s="1"/>
+      <c r="DH54" s="1"/>
+      <c r="DI54" s="1"/>
+      <c r="DJ54" s="1"/>
+      <c r="DK54" s="1"/>
+      <c r="DL54" s="1"/>
+      <c r="DM54" s="1"/>
+      <c r="DN54" s="1"/>
+      <c r="DO54" s="1"/>
+      <c r="DP54" s="1"/>
+      <c r="DQ54" s="1"/>
+      <c r="DR54" s="1"/>
+      <c r="DS54" s="1"/>
+      <c r="DT54" s="1"/>
+      <c r="DU54" s="1"/>
+      <c r="DV54" s="1"/>
+      <c r="DW54" s="1"/>
+      <c r="DX54" s="1"/>
+      <c r="DY54" s="1"/>
+      <c r="DZ54" s="1"/>
+      <c r="EA54" s="1"/>
+      <c r="EB54" s="1"/>
+      <c r="EC54" s="1"/>
+      <c r="ED54" s="1"/>
+      <c r="EE54" s="1"/>
+      <c r="EF54" s="1"/>
+      <c r="EG54" s="1"/>
+      <c r="EH54" s="1"/>
+      <c r="EI54" s="1"/>
+      <c r="EJ54" s="1"/>
+      <c r="EK54" s="1"/>
+      <c r="EL54" s="1"/>
+      <c r="EM54" s="1"/>
+      <c r="EN54" s="1"/>
+      <c r="EO54" s="1"/>
+      <c r="EP54" s="1"/>
+      <c r="EQ54" s="1"/>
+      <c r="ER54" s="1"/>
+      <c r="ES54" s="1"/>
+      <c r="ET54" s="1"/>
+      <c r="EU54" s="1"/>
+      <c r="EV54" s="1"/>
+      <c r="EW54" s="1"/>
+      <c r="EX54" s="1"/>
+      <c r="EY54" s="1"/>
+      <c r="EZ54" s="1"/>
+      <c r="FA54" s="1"/>
+      <c r="FB54" s="1"/>
+      <c r="FC54" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD54" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="FE54" s="1"/>
+      <c r="FF54" s="1"/>
+      <c r="FG54" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="FH54" s="1"/>
+      <c r="FI54" s="1"/>
+      <c r="FJ54" s="1"/>
+      <c r="FK54" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL54" s="1"/>
+      <c r="FM54" s="1"/>
+      <c r="FN54" s="1"/>
+      <c r="FO54" s="1"/>
+      <c r="FP54" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="FQ54" s="1"/>
+      <c r="FR54" s="1"/>
+      <c r="FS54" s="1">
+        <v>-22.946669439700699</v>
+      </c>
+      <c r="FT54" s="1">
+        <v>-45.960586862013898</v>
+      </c>
+      <c r="FU54" s="1"/>
+      <c r="FV54" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW54" s="1"/>
+      <c r="FX54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY54" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ54" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="GA54" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="GB54" s="1"/>
+      <c r="GC54" s="1"/>
+      <c r="GD54" s="1"/>
+      <c r="GE54" s="1"/>
+      <c r="GF54" s="1"/>
+      <c r="GG54" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH54" s="1"/>
+      <c r="GI54" s="1"/>
+      <c r="GJ54" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL54" s="1"/>
+      <c r="GM54" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN54" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO54" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G55" s="1">
+        <v>46135</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-22.928246999999999</v>
+      </c>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1">
+        <v>-45.969341999999997</v>
+      </c>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1">
+        <v>60</v>
+      </c>
+      <c r="AB55" s="1">
+        <v>-22.927888800000002</v>
+      </c>
+      <c r="AC55" s="1">
+        <v>-45.9686947</v>
+      </c>
+      <c r="AD55" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE55" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF55" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="AG55" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH55" s="1">
+        <v>1295</v>
+      </c>
+      <c r="AI55" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AL55" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM55" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN55" s="1"/>
+      <c r="AO55" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP55" s="1"/>
+      <c r="AQ55" s="1">
+        <v>-22.9279546</v>
+      </c>
+      <c r="AR55" s="1">
+        <v>-45.9687488</v>
+      </c>
+      <c r="AS55" s="1"/>
+      <c r="AT55" s="1"/>
+      <c r="AU55" s="1"/>
+      <c r="AV55" s="1"/>
+      <c r="AW55" s="1"/>
+      <c r="AX55" s="1"/>
+      <c r="AY55" s="1"/>
+      <c r="AZ55" s="1"/>
+      <c r="BA55" s="1"/>
+      <c r="BB55" s="1"/>
+      <c r="BC55" s="1"/>
+      <c r="BD55" s="1"/>
+      <c r="BE55" s="1"/>
+      <c r="BF55" s="1"/>
+      <c r="BG55" s="1"/>
+      <c r="BH55" s="1"/>
+      <c r="BI55" s="1"/>
+      <c r="BJ55" s="1"/>
+      <c r="BK55" s="1"/>
+      <c r="BL55" s="1"/>
+      <c r="BM55" s="1"/>
+      <c r="BN55" s="1"/>
+      <c r="BO55" s="1"/>
+      <c r="BP55" s="1"/>
+      <c r="BQ55" s="1"/>
+      <c r="BR55" s="1"/>
+      <c r="BS55" s="1"/>
+      <c r="BT55" s="1"/>
+      <c r="BU55" s="1"/>
+      <c r="BV55" s="1"/>
+      <c r="BW55" s="1"/>
+      <c r="BX55" s="1"/>
+      <c r="BY55" s="1"/>
+      <c r="BZ55" s="1"/>
+      <c r="CA55" s="1"/>
+      <c r="CB55" s="1"/>
+      <c r="CC55" s="1"/>
+      <c r="CD55" s="1"/>
+      <c r="CE55" s="1"/>
+      <c r="CF55" s="1"/>
+      <c r="CG55" s="1"/>
+      <c r="CH55" s="1"/>
+      <c r="CI55" s="1"/>
+      <c r="CJ55" s="1"/>
+      <c r="CK55" s="1"/>
+      <c r="CL55" s="1"/>
+      <c r="CM55" s="1"/>
+      <c r="CN55" s="1"/>
+      <c r="CO55" s="1"/>
+      <c r="CP55" s="1"/>
+      <c r="CQ55" s="1"/>
+      <c r="CR55" s="1"/>
+      <c r="CS55" s="1"/>
+      <c r="CT55" s="1"/>
+      <c r="CU55" s="1"/>
+      <c r="CV55" s="1"/>
+      <c r="CW55" s="1"/>
+      <c r="CX55" s="1"/>
+      <c r="CY55" s="1"/>
+      <c r="CZ55" s="1"/>
+      <c r="DA55" s="1"/>
+      <c r="DB55" s="1"/>
+      <c r="DC55" s="1"/>
+      <c r="DD55" s="1"/>
+      <c r="DE55" s="1"/>
+      <c r="DF55" s="1"/>
+      <c r="DG55" s="1"/>
+      <c r="DH55" s="1"/>
+      <c r="DI55" s="1"/>
+      <c r="DJ55" s="1"/>
+      <c r="DK55" s="1"/>
+      <c r="DL55" s="1"/>
+      <c r="DM55" s="1"/>
+      <c r="DN55" s="1"/>
+      <c r="DO55" s="1"/>
+      <c r="DP55" s="1"/>
+      <c r="DQ55" s="1"/>
+      <c r="DR55" s="1"/>
+      <c r="DS55" s="1"/>
+      <c r="DT55" s="1"/>
+      <c r="DU55" s="1"/>
+      <c r="DV55" s="1"/>
+      <c r="DW55" s="1"/>
+      <c r="DX55" s="1"/>
+      <c r="DY55" s="1"/>
+      <c r="DZ55" s="1"/>
+      <c r="EA55" s="1"/>
+      <c r="EB55" s="1"/>
+      <c r="EC55" s="1"/>
+      <c r="ED55" s="1"/>
+      <c r="EE55" s="1"/>
+      <c r="EF55" s="1"/>
+      <c r="EG55" s="1"/>
+      <c r="EH55" s="1"/>
+      <c r="EI55" s="1"/>
+      <c r="EJ55" s="1"/>
+      <c r="EK55" s="1"/>
+      <c r="EL55" s="1"/>
+      <c r="EM55" s="1"/>
+      <c r="EN55" s="1"/>
+      <c r="EO55" s="1"/>
+      <c r="EP55" s="1"/>
+      <c r="EQ55" s="1"/>
+      <c r="ER55" s="1"/>
+      <c r="ES55" s="1"/>
+      <c r="ET55" s="1"/>
+      <c r="EU55" s="1"/>
+      <c r="EV55" s="1"/>
+      <c r="EW55" s="1"/>
+      <c r="EX55" s="1"/>
+      <c r="EY55" s="1"/>
+      <c r="EZ55" s="1"/>
+      <c r="FA55" s="1"/>
+      <c r="FB55" s="1"/>
+      <c r="FC55" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD55" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="FE55" s="1"/>
+      <c r="FF55" s="1"/>
+      <c r="FG55" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="FH55" s="1"/>
+      <c r="FI55" s="1"/>
+      <c r="FJ55" s="1"/>
+      <c r="FK55" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL55" s="1"/>
+      <c r="FM55" s="1"/>
+      <c r="FN55" s="1"/>
+      <c r="FO55" s="1"/>
+      <c r="FP55" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="FQ55" s="1"/>
+      <c r="FR55" s="1"/>
+      <c r="FS55" s="1">
+        <v>-22.944800219270501</v>
+      </c>
+      <c r="FT55" s="1">
+        <v>-45.984118546672697</v>
+      </c>
+      <c r="FU55" s="1"/>
+      <c r="FV55" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW55" s="1"/>
+      <c r="FX55" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY55" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ55" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="GA55" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="GB55" s="1"/>
+      <c r="GC55" s="1"/>
+      <c r="GD55" s="1"/>
+      <c r="GE55" s="1"/>
+      <c r="GF55" s="1"/>
+      <c r="GG55" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH55" s="1"/>
+      <c r="GI55" s="1"/>
+      <c r="GJ55" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL55" s="1"/>
+      <c r="GM55" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN55" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO55" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:197" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="G56" s="6">
+        <v>46148</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J56" s="6">
+        <v>-22.936218</v>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6">
+        <v>-45.932715000000002</v>
+      </c>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="V56" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="W56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="X56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6">
+        <v>50</v>
+      </c>
+      <c r="AB56" s="6">
+        <v>-22.9362137</v>
+      </c>
+      <c r="AC56" s="6">
+        <v>-45.932694300000001</v>
+      </c>
+      <c r="AD56" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE56" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF56" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH56" s="6"/>
+      <c r="AI56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ56" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AK56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL56" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AM56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN56" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AO56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP56" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="AQ56" s="6">
+        <v>-22.936224200000002</v>
+      </c>
+      <c r="AR56" s="6">
+        <v>-45.9326559</v>
+      </c>
+      <c r="AS56" s="6"/>
+      <c r="AT56" s="6"/>
+      <c r="AU56" s="6"/>
+      <c r="AV56" s="6"/>
+      <c r="AW56" s="6"/>
+      <c r="AX56" s="6"/>
+      <c r="AY56" s="6"/>
+      <c r="AZ56" s="6"/>
+      <c r="BA56" s="6"/>
+      <c r="BB56" s="6"/>
+      <c r="BC56" s="6"/>
+      <c r="BD56" s="6"/>
+      <c r="BE56" s="6"/>
+      <c r="BF56" s="6"/>
+      <c r="BG56" s="6"/>
+      <c r="BH56" s="6"/>
+      <c r="BI56" s="6"/>
+      <c r="BJ56" s="6"/>
+      <c r="BK56" s="6"/>
+      <c r="BL56" s="6"/>
+      <c r="BM56" s="6"/>
+      <c r="BN56" s="6"/>
+      <c r="BO56" s="6"/>
+      <c r="BP56" s="6"/>
+      <c r="BQ56" s="6"/>
+      <c r="BR56" s="6"/>
+      <c r="BS56" s="6"/>
+      <c r="BT56" s="6"/>
+      <c r="BU56" s="6"/>
+      <c r="BV56" s="6"/>
+      <c r="BW56" s="6"/>
+      <c r="BX56" s="6"/>
+      <c r="BY56" s="6"/>
+      <c r="BZ56" s="6"/>
+      <c r="CA56" s="6"/>
+      <c r="CB56" s="6"/>
+      <c r="CC56" s="6"/>
+      <c r="CD56" s="6"/>
+      <c r="CE56" s="6"/>
+      <c r="CF56" s="6"/>
+      <c r="CG56" s="6"/>
+      <c r="CH56" s="6"/>
+      <c r="CI56" s="6"/>
+      <c r="CJ56" s="6"/>
+      <c r="CK56" s="6"/>
+      <c r="CL56" s="6"/>
+      <c r="CM56" s="6"/>
+      <c r="CN56" s="6"/>
+      <c r="CO56" s="6"/>
+      <c r="CP56" s="6"/>
+      <c r="CQ56" s="6"/>
+      <c r="CR56" s="6"/>
+      <c r="CS56" s="6"/>
+      <c r="CT56" s="6"/>
+      <c r="CU56" s="6"/>
+      <c r="CV56" s="6"/>
+      <c r="CW56" s="6"/>
+      <c r="CX56" s="6"/>
+      <c r="CY56" s="6"/>
+      <c r="CZ56" s="6"/>
+      <c r="DA56" s="6"/>
+      <c r="DB56" s="6"/>
+      <c r="DC56" s="6"/>
+      <c r="DD56" s="6"/>
+      <c r="DE56" s="6"/>
+      <c r="DF56" s="6"/>
+      <c r="DG56" s="6"/>
+      <c r="DH56" s="6"/>
+      <c r="DI56" s="6"/>
+      <c r="DJ56" s="6"/>
+      <c r="DK56" s="6"/>
+      <c r="DL56" s="6"/>
+      <c r="DM56" s="6"/>
+      <c r="DN56" s="6"/>
+      <c r="DO56" s="6"/>
+      <c r="DP56" s="6"/>
+      <c r="DQ56" s="6"/>
+      <c r="DR56" s="6"/>
+      <c r="DS56" s="6"/>
+      <c r="DT56" s="6"/>
+      <c r="DU56" s="6"/>
+      <c r="DV56" s="6"/>
+      <c r="DW56" s="6"/>
+      <c r="DX56" s="6"/>
+      <c r="DY56" s="6"/>
+      <c r="DZ56" s="6"/>
+      <c r="EA56" s="6"/>
+      <c r="EB56" s="6"/>
+      <c r="EC56" s="6"/>
+      <c r="ED56" s="6"/>
+      <c r="EE56" s="6"/>
+      <c r="EF56" s="6"/>
+      <c r="EG56" s="6"/>
+      <c r="EH56" s="6"/>
+      <c r="EI56" s="6"/>
+      <c r="EJ56" s="6"/>
+      <c r="EK56" s="6"/>
+      <c r="EL56" s="6"/>
+      <c r="EM56" s="6"/>
+      <c r="EN56" s="6"/>
+      <c r="EO56" s="6"/>
+      <c r="EP56" s="6"/>
+      <c r="EQ56" s="6"/>
+      <c r="ER56" s="6"/>
+      <c r="ES56" s="6"/>
+      <c r="ET56" s="6"/>
+      <c r="EU56" s="6"/>
+      <c r="EV56" s="6"/>
+      <c r="EW56" s="6"/>
+      <c r="EX56" s="6"/>
+      <c r="EY56" s="6"/>
+      <c r="EZ56" s="6"/>
+      <c r="FA56" s="6"/>
+      <c r="FB56" s="6"/>
+      <c r="FC56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD56" s="6"/>
+      <c r="FE56" s="6"/>
+      <c r="FF56" s="6"/>
+      <c r="FG56" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="FH56" s="6"/>
+      <c r="FI56" s="6"/>
+      <c r="FJ56" s="6"/>
+      <c r="FK56" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL56" s="6"/>
+      <c r="FM56" s="6"/>
+      <c r="FN56" s="6"/>
+      <c r="FO56" s="6"/>
+      <c r="FP56" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="FQ56" s="6"/>
+      <c r="FR56" s="6"/>
+      <c r="FS56" s="6">
+        <v>-22.9144504504739</v>
+      </c>
+      <c r="FT56" s="6">
+        <v>-45.953700003562098</v>
+      </c>
+      <c r="FU56" s="6"/>
+      <c r="FV56" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW56" s="6"/>
+      <c r="FX56" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY56" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="FZ56" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="GA56" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="GB56" s="6"/>
+      <c r="GC56" s="6"/>
+      <c r="GD56" s="6"/>
+      <c r="GE56" s="6"/>
+      <c r="GF56" s="6"/>
+      <c r="GG56" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="GH56" s="6"/>
+      <c r="GI56" s="6"/>
+      <c r="GJ56" s="6">
+        <v>1</v>
+      </c>
+      <c r="GK56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL56" s="6"/>
+      <c r="GM56" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN56" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO56" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1">
+        <v>46171</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J57" s="1">
+        <v>-22.910423999999999</v>
+      </c>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1">
+        <v>-46.000855999999999</v>
+      </c>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X57" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1">
+        <v>500</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>-22.910055100000001</v>
+      </c>
+      <c r="AC57" s="1">
+        <v>-46.001041000000001</v>
+      </c>
+      <c r="AD57" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE57" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF57" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ57" s="1"/>
+      <c r="AK57" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AM57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN57" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO57" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP57" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="AQ57" s="1">
+        <v>-22.9103049</v>
+      </c>
+      <c r="AR57" s="1">
+        <v>-46.000889899999997</v>
+      </c>
+      <c r="AS57" s="1"/>
+      <c r="AT57" s="1"/>
+      <c r="AU57" s="1"/>
+      <c r="AV57" s="1"/>
+      <c r="AW57" s="1"/>
+      <c r="AX57" s="1"/>
+      <c r="AY57" s="1"/>
+      <c r="AZ57" s="1"/>
+      <c r="BA57" s="1"/>
+      <c r="BB57" s="1"/>
+      <c r="BC57" s="1"/>
+      <c r="BD57" s="1"/>
+      <c r="BE57" s="1"/>
+      <c r="BF57" s="1"/>
+      <c r="BG57" s="1"/>
+      <c r="BH57" s="1"/>
+      <c r="BI57" s="1"/>
+      <c r="BJ57" s="1"/>
+      <c r="BK57" s="1"/>
+      <c r="BL57" s="1"/>
+      <c r="BM57" s="1"/>
+      <c r="BN57" s="1"/>
+      <c r="BO57" s="1"/>
+      <c r="BP57" s="1"/>
+      <c r="BQ57" s="1"/>
+      <c r="BR57" s="1"/>
+      <c r="BS57" s="1"/>
+      <c r="BT57" s="1"/>
+      <c r="BU57" s="1"/>
+      <c r="BV57" s="1"/>
+      <c r="BW57" s="1"/>
+      <c r="BX57" s="1"/>
+      <c r="BY57" s="1"/>
+      <c r="BZ57" s="1"/>
+      <c r="CA57" s="1"/>
+      <c r="CB57" s="1"/>
+      <c r="CC57" s="1"/>
+      <c r="CD57" s="1"/>
+      <c r="CE57" s="1"/>
+      <c r="CF57" s="1"/>
+      <c r="CG57" s="1"/>
+      <c r="CH57" s="1"/>
+      <c r="CI57" s="1"/>
+      <c r="CJ57" s="1"/>
+      <c r="CK57" s="1"/>
+      <c r="CL57" s="1"/>
+      <c r="CM57" s="1"/>
+      <c r="CN57" s="1"/>
+      <c r="CO57" s="1"/>
+      <c r="CP57" s="1"/>
+      <c r="CQ57" s="1"/>
+      <c r="CR57" s="1"/>
+      <c r="CS57" s="1"/>
+      <c r="CT57" s="1"/>
+      <c r="CU57" s="1"/>
+      <c r="CV57" s="1"/>
+      <c r="CW57" s="1"/>
+      <c r="CX57" s="1"/>
+      <c r="CY57" s="1"/>
+      <c r="CZ57" s="1"/>
+      <c r="DA57" s="1"/>
+      <c r="DB57" s="1"/>
+      <c r="DC57" s="1"/>
+      <c r="DD57" s="1"/>
+      <c r="DE57" s="1"/>
+      <c r="DF57" s="1"/>
+      <c r="DG57" s="1"/>
+      <c r="DH57" s="1"/>
+      <c r="DI57" s="1"/>
+      <c r="DJ57" s="1"/>
+      <c r="DK57" s="1"/>
+      <c r="DL57" s="1"/>
+      <c r="DM57" s="1"/>
+      <c r="DN57" s="1"/>
+      <c r="DO57" s="1"/>
+      <c r="DP57" s="1"/>
+      <c r="DQ57" s="1"/>
+      <c r="DR57" s="1"/>
+      <c r="DS57" s="1"/>
+      <c r="DT57" s="1"/>
+      <c r="DU57" s="1"/>
+      <c r="DV57" s="1"/>
+      <c r="DW57" s="1"/>
+      <c r="DX57" s="1"/>
+      <c r="DY57" s="1"/>
+      <c r="DZ57" s="1"/>
+      <c r="EA57" s="1"/>
+      <c r="EB57" s="1"/>
+      <c r="EC57" s="1"/>
+      <c r="ED57" s="1"/>
+      <c r="EE57" s="1"/>
+      <c r="EF57" s="1"/>
+      <c r="EG57" s="1"/>
+      <c r="EH57" s="1"/>
+      <c r="EI57" s="1"/>
+      <c r="EJ57" s="1"/>
+      <c r="EK57" s="1"/>
+      <c r="EL57" s="1"/>
+      <c r="EM57" s="1"/>
+      <c r="EN57" s="1"/>
+      <c r="EO57" s="1"/>
+      <c r="EP57" s="1"/>
+      <c r="EQ57" s="1"/>
+      <c r="ER57" s="1"/>
+      <c r="ES57" s="1"/>
+      <c r="ET57" s="1"/>
+      <c r="EU57" s="1"/>
+      <c r="EV57" s="1"/>
+      <c r="EW57" s="1"/>
+      <c r="EX57" s="1"/>
+      <c r="EY57" s="1"/>
+      <c r="EZ57" s="1"/>
+      <c r="FA57" s="1"/>
+      <c r="FB57" s="1"/>
+      <c r="FC57" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD57" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="FE57" s="1"/>
+      <c r="FF57" s="1"/>
+      <c r="FG57" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="FH57" s="1"/>
+      <c r="FI57" s="1"/>
+      <c r="FJ57" s="1"/>
+      <c r="FK57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL57" s="1"/>
+      <c r="FM57" s="1"/>
+      <c r="FN57" s="1"/>
+      <c r="FO57" s="1"/>
+      <c r="FP57" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="FQ57" s="1"/>
+      <c r="FR57" s="1"/>
+      <c r="FS57" s="1">
+        <v>-22.915160568548298</v>
+      </c>
+      <c r="FT57" s="1">
+        <v>-46.009712190787802</v>
+      </c>
+      <c r="FU57" s="1"/>
+      <c r="FV57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW57" s="1"/>
+      <c r="FX57" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY57" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="FZ57" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="GA57" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="GB57" s="1"/>
+      <c r="GC57" s="1"/>
+      <c r="GD57" s="1"/>
+      <c r="GE57" s="1"/>
+      <c r="GF57" s="1"/>
+      <c r="GG57" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH57" s="1"/>
+      <c r="GI57" s="1"/>
+      <c r="GJ57" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL57" s="1"/>
+      <c r="GM57" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN57" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO57" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G58" s="1">
+        <v>46171</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J58" s="1">
+        <v>-22.920950000000001</v>
+      </c>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1">
+        <v>-46.006014999999998</v>
+      </c>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="W58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1">
+        <v>50</v>
+      </c>
+      <c r="AB58" s="1">
+        <v>-22.921104100000001</v>
+      </c>
+      <c r="AC58" s="1">
+        <v>-46.006032400000002</v>
+      </c>
+      <c r="AD58" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE58" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF58" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH58" s="1"/>
+      <c r="AI58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ58" s="1"/>
+      <c r="AK58" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL58" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AM58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN58" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO58" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP58" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AQ58" s="1">
+        <v>-22.921065299999999</v>
+      </c>
+      <c r="AR58" s="1">
+        <v>-46.006052199999999</v>
+      </c>
+      <c r="AS58" s="1"/>
+      <c r="AT58" s="1"/>
+      <c r="AU58" s="1"/>
+      <c r="AV58" s="1"/>
+      <c r="AW58" s="1"/>
+      <c r="AX58" s="1"/>
+      <c r="AY58" s="1"/>
+      <c r="AZ58" s="1"/>
+      <c r="BA58" s="1"/>
+      <c r="BB58" s="1"/>
+      <c r="BC58" s="1"/>
+      <c r="BD58" s="1"/>
+      <c r="BE58" s="1"/>
+      <c r="BF58" s="1"/>
+      <c r="BG58" s="1"/>
+      <c r="BH58" s="1"/>
+      <c r="BI58" s="1"/>
+      <c r="BJ58" s="1"/>
+      <c r="BK58" s="1"/>
+      <c r="BL58" s="1"/>
+      <c r="BM58" s="1"/>
+      <c r="BN58" s="1"/>
+      <c r="BO58" s="1"/>
+      <c r="BP58" s="1"/>
+      <c r="BQ58" s="1"/>
+      <c r="BR58" s="1"/>
+      <c r="BS58" s="1"/>
+      <c r="BT58" s="1"/>
+      <c r="BU58" s="1"/>
+      <c r="BV58" s="1"/>
+      <c r="BW58" s="1"/>
+      <c r="BX58" s="1"/>
+      <c r="BY58" s="1"/>
+      <c r="BZ58" s="1"/>
+      <c r="CA58" s="1"/>
+      <c r="CB58" s="1"/>
+      <c r="CC58" s="1"/>
+      <c r="CD58" s="1"/>
+      <c r="CE58" s="1"/>
+      <c r="CF58" s="1"/>
+      <c r="CG58" s="1"/>
+      <c r="CH58" s="1"/>
+      <c r="CI58" s="1"/>
+      <c r="CJ58" s="1"/>
+      <c r="CK58" s="1"/>
+      <c r="CL58" s="1"/>
+      <c r="CM58" s="1"/>
+      <c r="CN58" s="1"/>
+      <c r="CO58" s="1"/>
+      <c r="CP58" s="1"/>
+      <c r="CQ58" s="1"/>
+      <c r="CR58" s="1"/>
+      <c r="CS58" s="1"/>
+      <c r="CT58" s="1"/>
+      <c r="CU58" s="1"/>
+      <c r="CV58" s="1"/>
+      <c r="CW58" s="1"/>
+      <c r="CX58" s="1"/>
+      <c r="CY58" s="1"/>
+      <c r="CZ58" s="1"/>
+      <c r="DA58" s="1"/>
+      <c r="DB58" s="1"/>
+      <c r="DC58" s="1"/>
+      <c r="DD58" s="1"/>
+      <c r="DE58" s="1"/>
+      <c r="DF58" s="1"/>
+      <c r="DG58" s="1"/>
+      <c r="DH58" s="1"/>
+      <c r="DI58" s="1"/>
+      <c r="DJ58" s="1"/>
+      <c r="DK58" s="1"/>
+      <c r="DL58" s="1"/>
+      <c r="DM58" s="1"/>
+      <c r="DN58" s="1"/>
+      <c r="DO58" s="1"/>
+      <c r="DP58" s="1"/>
+      <c r="DQ58" s="1"/>
+      <c r="DR58" s="1"/>
+      <c r="DS58" s="1"/>
+      <c r="DT58" s="1"/>
+      <c r="DU58" s="1"/>
+      <c r="DV58" s="1"/>
+      <c r="DW58" s="1"/>
+      <c r="DX58" s="1"/>
+      <c r="DY58" s="1"/>
+      <c r="DZ58" s="1"/>
+      <c r="EA58" s="1"/>
+      <c r="EB58" s="1"/>
+      <c r="EC58" s="1"/>
+      <c r="ED58" s="1"/>
+      <c r="EE58" s="1"/>
+      <c r="EF58" s="1"/>
+      <c r="EG58" s="1"/>
+      <c r="EH58" s="1"/>
+      <c r="EI58" s="1"/>
+      <c r="EJ58" s="1"/>
+      <c r="EK58" s="1"/>
+      <c r="EL58" s="1"/>
+      <c r="EM58" s="1"/>
+      <c r="EN58" s="1"/>
+      <c r="EO58" s="1"/>
+      <c r="EP58" s="1"/>
+      <c r="EQ58" s="1"/>
+      <c r="ER58" s="1"/>
+      <c r="ES58" s="1"/>
+      <c r="ET58" s="1"/>
+      <c r="EU58" s="1"/>
+      <c r="EV58" s="1"/>
+      <c r="EW58" s="1"/>
+      <c r="EX58" s="1"/>
+      <c r="EY58" s="1"/>
+      <c r="EZ58" s="1"/>
+      <c r="FA58" s="1"/>
+      <c r="FB58" s="1"/>
+      <c r="FC58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD58" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="FE58" s="1"/>
+      <c r="FF58" s="1"/>
+      <c r="FG58" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="FH58" s="1"/>
+      <c r="FI58" s="1"/>
+      <c r="FJ58" s="1"/>
+      <c r="FK58" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL58" s="1"/>
+      <c r="FM58" s="1"/>
+      <c r="FN58" s="1"/>
+      <c r="FO58" s="1"/>
+      <c r="FP58" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="FQ58" s="1"/>
+      <c r="FR58" s="1"/>
+      <c r="FS58" s="1">
+        <v>-22.915160568548298</v>
+      </c>
+      <c r="FT58" s="1">
+        <v>-46.009712190787802</v>
+      </c>
+      <c r="FU58" s="1"/>
+      <c r="FV58" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW58" s="1"/>
+      <c r="FX58" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY58" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="FZ58" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="GA58" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="GB58" s="1"/>
+      <c r="GC58" s="1"/>
+      <c r="GD58" s="1"/>
+      <c r="GE58" s="1"/>
+      <c r="GF58" s="1"/>
+      <c r="GG58" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH58" s="1"/>
+      <c r="GI58" s="1"/>
+      <c r="GJ58" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL58" s="1"/>
+      <c r="GM58" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN58" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO58" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G59" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J59" s="1">
+        <v>-22.850884000000001</v>
+      </c>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1">
+        <v>-45.928733000000001</v>
+      </c>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="1">
+        <v>-22.850901400000001</v>
+      </c>
+      <c r="AC59" s="1">
+        <v>-45.928720599999998</v>
+      </c>
+      <c r="AD59" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE59" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF59" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG59" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH59" s="1"/>
+      <c r="AI59" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ59" s="1"/>
+      <c r="AK59" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL59" s="1"/>
+      <c r="AM59" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN59" s="1"/>
+      <c r="AO59" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP59" s="1"/>
+      <c r="AQ59" s="1">
+        <v>-22.850910599999999</v>
+      </c>
+      <c r="AR59" s="1">
+        <v>-45.928714200000002</v>
+      </c>
+      <c r="AS59" s="1"/>
+      <c r="AT59" s="1"/>
+      <c r="AU59" s="1"/>
+      <c r="AV59" s="1"/>
+      <c r="AW59" s="1"/>
+      <c r="AX59" s="1"/>
+      <c r="AY59" s="1"/>
+      <c r="AZ59" s="1"/>
+      <c r="BA59" s="1"/>
+      <c r="BB59" s="1"/>
+      <c r="BC59" s="1"/>
+      <c r="BD59" s="1"/>
+      <c r="BE59" s="1"/>
+      <c r="BF59" s="1"/>
+      <c r="BG59" s="1"/>
+      <c r="BH59" s="1"/>
+      <c r="BI59" s="1"/>
+      <c r="BJ59" s="1"/>
+      <c r="BK59" s="1"/>
+      <c r="BL59" s="1"/>
+      <c r="BM59" s="1"/>
+      <c r="BN59" s="1"/>
+      <c r="BO59" s="1"/>
+      <c r="BP59" s="1"/>
+      <c r="BQ59" s="1"/>
+      <c r="BR59" s="1"/>
+      <c r="BS59" s="1"/>
+      <c r="BT59" s="1"/>
+      <c r="BU59" s="1"/>
+      <c r="BV59" s="1"/>
+      <c r="BW59" s="1"/>
+      <c r="BX59" s="1"/>
+      <c r="BY59" s="1"/>
+      <c r="BZ59" s="1"/>
+      <c r="CA59" s="1"/>
+      <c r="CB59" s="1"/>
+      <c r="CC59" s="1"/>
+      <c r="CD59" s="1"/>
+      <c r="CE59" s="1"/>
+      <c r="CF59" s="1"/>
+      <c r="CG59" s="1"/>
+      <c r="CH59" s="1"/>
+      <c r="CI59" s="1"/>
+      <c r="CJ59" s="1"/>
+      <c r="CK59" s="1"/>
+      <c r="CL59" s="1"/>
+      <c r="CM59" s="1"/>
+      <c r="CN59" s="1"/>
+      <c r="CO59" s="1"/>
+      <c r="CP59" s="1"/>
+      <c r="CQ59" s="1"/>
+      <c r="CR59" s="1"/>
+      <c r="CS59" s="1"/>
+      <c r="CT59" s="1"/>
+      <c r="CU59" s="1"/>
+      <c r="CV59" s="1"/>
+      <c r="CW59" s="1"/>
+      <c r="CX59" s="1"/>
+      <c r="CY59" s="1"/>
+      <c r="CZ59" s="1"/>
+      <c r="DA59" s="1"/>
+      <c r="DB59" s="1"/>
+      <c r="DC59" s="1"/>
+      <c r="DD59" s="1"/>
+      <c r="DE59" s="1"/>
+      <c r="DF59" s="1"/>
+      <c r="DG59" s="1"/>
+      <c r="DH59" s="1"/>
+      <c r="DI59" s="1"/>
+      <c r="DJ59" s="1"/>
+      <c r="DK59" s="1"/>
+      <c r="DL59" s="1"/>
+      <c r="DM59" s="1"/>
+      <c r="DN59" s="1"/>
+      <c r="DO59" s="1"/>
+      <c r="DP59" s="1"/>
+      <c r="DQ59" s="1"/>
+      <c r="DR59" s="1"/>
+      <c r="DS59" s="1"/>
+      <c r="DT59" s="1"/>
+      <c r="DU59" s="1"/>
+      <c r="DV59" s="1"/>
+      <c r="DW59" s="1"/>
+      <c r="DX59" s="1"/>
+      <c r="DY59" s="1"/>
+      <c r="DZ59" s="1"/>
+      <c r="EA59" s="1"/>
+      <c r="EB59" s="1"/>
+      <c r="EC59" s="1"/>
+      <c r="ED59" s="1"/>
+      <c r="EE59" s="1"/>
+      <c r="EF59" s="1"/>
+      <c r="EG59" s="1"/>
+      <c r="EH59" s="1"/>
+      <c r="EI59" s="1"/>
+      <c r="EJ59" s="1"/>
+      <c r="EK59" s="1"/>
+      <c r="EL59" s="1"/>
+      <c r="EM59" s="1"/>
+      <c r="EN59" s="1"/>
+      <c r="EO59" s="1"/>
+      <c r="EP59" s="1"/>
+      <c r="EQ59" s="1"/>
+      <c r="ER59" s="1"/>
+      <c r="ES59" s="1"/>
+      <c r="ET59" s="1"/>
+      <c r="EU59" s="1"/>
+      <c r="EV59" s="1"/>
+      <c r="EW59" s="1"/>
+      <c r="EX59" s="1"/>
+      <c r="EY59" s="1"/>
+      <c r="EZ59" s="1"/>
+      <c r="FA59" s="1"/>
+      <c r="FB59" s="1"/>
+      <c r="FC59" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD59" s="1"/>
+      <c r="FE59" s="1"/>
+      <c r="FF59" s="1"/>
+      <c r="FG59" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="FH59" s="1"/>
+      <c r="FI59" s="1"/>
+      <c r="FJ59" s="1"/>
+      <c r="FK59" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL59" s="1"/>
+      <c r="FM59" s="1"/>
+      <c r="FN59" s="1"/>
+      <c r="FO59" s="1"/>
+      <c r="FP59" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="FQ59" s="1"/>
+      <c r="FR59" s="1"/>
+      <c r="FS59" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT59" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU59" s="1"/>
+      <c r="FV59" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW59" s="1"/>
+      <c r="FX59" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY59" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ59" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="GA59" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="GB59" s="1"/>
+      <c r="GC59" s="1"/>
+      <c r="GD59" s="1"/>
+      <c r="GE59" s="1"/>
+      <c r="GF59" s="1"/>
+      <c r="GG59" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH59" s="1"/>
+      <c r="GI59" s="1"/>
+      <c r="GJ59" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL59" s="1"/>
+      <c r="GM59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN59" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO59" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G60" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J60" s="1">
+        <v>-22.855927999999999</v>
+      </c>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1">
+        <v>-45.933276999999997</v>
+      </c>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1">
+        <v>100</v>
+      </c>
+      <c r="AB60" s="1">
+        <v>-22.8553633</v>
+      </c>
+      <c r="AC60" s="1">
+        <v>-45.934085000000003</v>
+      </c>
+      <c r="AD60" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE60" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF60" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG60" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH60" s="1">
+        <v>2100</v>
+      </c>
+      <c r="AI60" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ60" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL60" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AM60" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN60" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AO60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP60" s="1"/>
+      <c r="AQ60" s="1"/>
+      <c r="AR60" s="1"/>
+      <c r="AS60" s="1"/>
+      <c r="AT60" s="1"/>
+      <c r="AU60" s="1"/>
+      <c r="AV60" s="1"/>
+      <c r="AW60" s="1"/>
+      <c r="AX60" s="1"/>
+      <c r="AY60" s="1"/>
+      <c r="AZ60" s="1"/>
+      <c r="BA60" s="1"/>
+      <c r="BB60" s="1"/>
+      <c r="BC60" s="1"/>
+      <c r="BD60" s="1"/>
+      <c r="BE60" s="1"/>
+      <c r="BF60" s="1"/>
+      <c r="BG60" s="1"/>
+      <c r="BH60" s="1"/>
+      <c r="BI60" s="1"/>
+      <c r="BJ60" s="1"/>
+      <c r="BK60" s="1"/>
+      <c r="BL60" s="1"/>
+      <c r="BM60" s="1"/>
+      <c r="BN60" s="1"/>
+      <c r="BO60" s="1"/>
+      <c r="BP60" s="1"/>
+      <c r="BQ60" s="1"/>
+      <c r="BR60" s="1"/>
+      <c r="BS60" s="1"/>
+      <c r="BT60" s="1"/>
+      <c r="BU60" s="1"/>
+      <c r="BV60" s="1"/>
+      <c r="BW60" s="1"/>
+      <c r="BX60" s="1"/>
+      <c r="BY60" s="1"/>
+      <c r="BZ60" s="1"/>
+      <c r="CA60" s="1"/>
+      <c r="CB60" s="1"/>
+      <c r="CC60" s="1"/>
+      <c r="CD60" s="1"/>
+      <c r="CE60" s="1"/>
+      <c r="CF60" s="1"/>
+      <c r="CG60" s="1"/>
+      <c r="CH60" s="1"/>
+      <c r="CI60" s="1"/>
+      <c r="CJ60" s="1"/>
+      <c r="CK60" s="1"/>
+      <c r="CL60" s="1"/>
+      <c r="CM60" s="1"/>
+      <c r="CN60" s="1"/>
+      <c r="CO60" s="1"/>
+      <c r="CP60" s="1"/>
+      <c r="CQ60" s="1"/>
+      <c r="CR60" s="1"/>
+      <c r="CS60" s="1"/>
+      <c r="CT60" s="1"/>
+      <c r="CU60" s="1"/>
+      <c r="CV60" s="1"/>
+      <c r="CW60" s="1"/>
+      <c r="CX60" s="1"/>
+      <c r="CY60" s="1"/>
+      <c r="CZ60" s="1"/>
+      <c r="DA60" s="1"/>
+      <c r="DB60" s="1"/>
+      <c r="DC60" s="1"/>
+      <c r="DD60" s="1"/>
+      <c r="DE60" s="1"/>
+      <c r="DF60" s="1"/>
+      <c r="DG60" s="1"/>
+      <c r="DH60" s="1"/>
+      <c r="DI60" s="1"/>
+      <c r="DJ60" s="1"/>
+      <c r="DK60" s="1"/>
+      <c r="DL60" s="1"/>
+      <c r="DM60" s="1"/>
+      <c r="DN60" s="1"/>
+      <c r="DO60" s="1"/>
+      <c r="DP60" s="1"/>
+      <c r="DQ60" s="1"/>
+      <c r="DR60" s="1"/>
+      <c r="DS60" s="1"/>
+      <c r="DT60" s="1"/>
+      <c r="DU60" s="1"/>
+      <c r="DV60" s="1"/>
+      <c r="DW60" s="1"/>
+      <c r="DX60" s="1"/>
+      <c r="DY60" s="1"/>
+      <c r="DZ60" s="1"/>
+      <c r="EA60" s="1"/>
+      <c r="EB60" s="1"/>
+      <c r="EC60" s="1"/>
+      <c r="ED60" s="1"/>
+      <c r="EE60" s="1"/>
+      <c r="EF60" s="1"/>
+      <c r="EG60" s="1"/>
+      <c r="EH60" s="1"/>
+      <c r="EI60" s="1"/>
+      <c r="EJ60" s="1"/>
+      <c r="EK60" s="1"/>
+      <c r="EL60" s="1"/>
+      <c r="EM60" s="1"/>
+      <c r="EN60" s="1"/>
+      <c r="EO60" s="1"/>
+      <c r="EP60" s="1"/>
+      <c r="EQ60" s="1"/>
+      <c r="ER60" s="1"/>
+      <c r="ES60" s="1"/>
+      <c r="ET60" s="1"/>
+      <c r="EU60" s="1"/>
+      <c r="EV60" s="1"/>
+      <c r="EW60" s="1"/>
+      <c r="EX60" s="1"/>
+      <c r="EY60" s="1"/>
+      <c r="EZ60" s="1"/>
+      <c r="FA60" s="1"/>
+      <c r="FB60" s="1"/>
+      <c r="FC60" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD60" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="FE60" s="1"/>
+      <c r="FF60" s="1"/>
+      <c r="FG60" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="FH60" s="1"/>
+      <c r="FI60" s="1"/>
+      <c r="FJ60" s="1"/>
+      <c r="FK60" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL60" s="1"/>
+      <c r="FM60" s="1"/>
+      <c r="FN60" s="1"/>
+      <c r="FO60" s="1"/>
+      <c r="FP60" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="FQ60" s="1"/>
+      <c r="FR60" s="1"/>
+      <c r="FS60" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT60" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU60" s="1"/>
+      <c r="FV60" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW60" s="1"/>
+      <c r="FX60" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY60" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ60" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="GA60" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="GB60" s="1"/>
+      <c r="GC60" s="1"/>
+      <c r="GD60" s="1"/>
+      <c r="GE60" s="1"/>
+      <c r="GF60" s="1"/>
+      <c r="GG60" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH60" s="1"/>
+      <c r="GI60" s="1"/>
+      <c r="GJ60" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL60" s="1"/>
+      <c r="GM60" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN60" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO60" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G61" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J61" s="1">
+        <v>-22.862606</v>
+      </c>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1">
+        <v>-45.931848000000002</v>
+      </c>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="1">
+        <v>-22.862584399999999</v>
+      </c>
+      <c r="AC61" s="1">
+        <v>-45.931886499999997</v>
+      </c>
+      <c r="AD61" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE61" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF61" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AG61" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH61" s="1">
+        <v>5600</v>
+      </c>
+      <c r="AI61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ61" s="1"/>
+      <c r="AK61" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL61" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="AM61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN61" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO61" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP61" s="1"/>
+      <c r="AQ61" s="1"/>
+      <c r="AR61" s="1"/>
+      <c r="AS61" s="1"/>
+      <c r="AT61" s="1"/>
+      <c r="AU61" s="1"/>
+      <c r="AV61" s="1"/>
+      <c r="AW61" s="1"/>
+      <c r="AX61" s="1"/>
+      <c r="AY61" s="1"/>
+      <c r="AZ61" s="1"/>
+      <c r="BA61" s="1"/>
+      <c r="BB61" s="1"/>
+      <c r="BC61" s="1"/>
+      <c r="BD61" s="1"/>
+      <c r="BE61" s="1"/>
+      <c r="BF61" s="1"/>
+      <c r="BG61" s="1"/>
+      <c r="BH61" s="1"/>
+      <c r="BI61" s="1"/>
+      <c r="BJ61" s="1"/>
+      <c r="BK61" s="1"/>
+      <c r="BL61" s="1"/>
+      <c r="BM61" s="1"/>
+      <c r="BN61" s="1"/>
+      <c r="BO61" s="1"/>
+      <c r="BP61" s="1"/>
+      <c r="BQ61" s="1"/>
+      <c r="BR61" s="1"/>
+      <c r="BS61" s="1"/>
+      <c r="BT61" s="1"/>
+      <c r="BU61" s="1"/>
+      <c r="BV61" s="1"/>
+      <c r="BW61" s="1"/>
+      <c r="BX61" s="1"/>
+      <c r="BY61" s="1"/>
+      <c r="BZ61" s="1"/>
+      <c r="CA61" s="1"/>
+      <c r="CB61" s="1"/>
+      <c r="CC61" s="1"/>
+      <c r="CD61" s="1"/>
+      <c r="CE61" s="1"/>
+      <c r="CF61" s="1"/>
+      <c r="CG61" s="1"/>
+      <c r="CH61" s="1"/>
+      <c r="CI61" s="1"/>
+      <c r="CJ61" s="1"/>
+      <c r="CK61" s="1"/>
+      <c r="CL61" s="1"/>
+      <c r="CM61" s="1"/>
+      <c r="CN61" s="1"/>
+      <c r="CO61" s="1"/>
+      <c r="CP61" s="1"/>
+      <c r="CQ61" s="1"/>
+      <c r="CR61" s="1"/>
+      <c r="CS61" s="1"/>
+      <c r="CT61" s="1"/>
+      <c r="CU61" s="1"/>
+      <c r="CV61" s="1"/>
+      <c r="CW61" s="1"/>
+      <c r="CX61" s="1"/>
+      <c r="CY61" s="1"/>
+      <c r="CZ61" s="1"/>
+      <c r="DA61" s="1"/>
+      <c r="DB61" s="1"/>
+      <c r="DC61" s="1"/>
+      <c r="DD61" s="1"/>
+      <c r="DE61" s="1"/>
+      <c r="DF61" s="1"/>
+      <c r="DG61" s="1"/>
+      <c r="DH61" s="1"/>
+      <c r="DI61" s="1"/>
+      <c r="DJ61" s="1"/>
+      <c r="DK61" s="1"/>
+      <c r="DL61" s="1"/>
+      <c r="DM61" s="1"/>
+      <c r="DN61" s="1"/>
+      <c r="DO61" s="1"/>
+      <c r="DP61" s="1"/>
+      <c r="DQ61" s="1"/>
+      <c r="DR61" s="1"/>
+      <c r="DS61" s="1"/>
+      <c r="DT61" s="1"/>
+      <c r="DU61" s="1"/>
+      <c r="DV61" s="1"/>
+      <c r="DW61" s="1"/>
+      <c r="DX61" s="1"/>
+      <c r="DY61" s="1"/>
+      <c r="DZ61" s="1"/>
+      <c r="EA61" s="1"/>
+      <c r="EB61" s="1"/>
+      <c r="EC61" s="1"/>
+      <c r="ED61" s="1"/>
+      <c r="EE61" s="1"/>
+      <c r="EF61" s="1"/>
+      <c r="EG61" s="1"/>
+      <c r="EH61" s="1"/>
+      <c r="EI61" s="1"/>
+      <c r="EJ61" s="1"/>
+      <c r="EK61" s="1"/>
+      <c r="EL61" s="1"/>
+      <c r="EM61" s="1"/>
+      <c r="EN61" s="1"/>
+      <c r="EO61" s="1"/>
+      <c r="EP61" s="1"/>
+      <c r="EQ61" s="1"/>
+      <c r="ER61" s="1"/>
+      <c r="ES61" s="1"/>
+      <c r="ET61" s="1"/>
+      <c r="EU61" s="1"/>
+      <c r="EV61" s="1"/>
+      <c r="EW61" s="1"/>
+      <c r="EX61" s="1"/>
+      <c r="EY61" s="1"/>
+      <c r="EZ61" s="1"/>
+      <c r="FA61" s="1"/>
+      <c r="FB61" s="1"/>
+      <c r="FC61" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD61" s="1"/>
+      <c r="FE61" s="1"/>
+      <c r="FF61" s="1"/>
+      <c r="FG61" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="FH61" s="1"/>
+      <c r="FI61" s="1"/>
+      <c r="FJ61" s="1"/>
+      <c r="FK61" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL61" s="1"/>
+      <c r="FM61" s="1"/>
+      <c r="FN61" s="1"/>
+      <c r="FO61" s="1"/>
+      <c r="FP61" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="FQ61" s="1"/>
+      <c r="FR61" s="1"/>
+      <c r="FS61" s="1">
+        <v>-22.8917700954084</v>
+      </c>
+      <c r="FT61" s="1">
+        <v>-45.951792921037203</v>
+      </c>
+      <c r="FU61" s="1"/>
+      <c r="FV61" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW61" s="1"/>
+      <c r="FX61" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY61" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="FZ61" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="GA61" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="GB61" s="1"/>
+      <c r="GC61" s="1"/>
+      <c r="GD61" s="1"/>
+      <c r="GE61" s="1"/>
+      <c r="GF61" s="1"/>
+      <c r="GG61" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH61" s="1"/>
+      <c r="GI61" s="1"/>
+      <c r="GJ61" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL61" s="1"/>
+      <c r="GM61" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN61" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO61" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G62" s="1">
+        <v>46134</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J62" s="1">
+        <v>-22.925559</v>
+      </c>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1">
+        <v>-45.983710000000002</v>
+      </c>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X62" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="1">
+        <v>-22.9255532</v>
+      </c>
+      <c r="AC62" s="1">
+        <v>-45.983625699999997</v>
+      </c>
+      <c r="AD62" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE62" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF62" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AG62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ62" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AK62" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL62" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AM62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN62" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO62" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP62" s="1"/>
+      <c r="AQ62" s="1"/>
+      <c r="AR62" s="1"/>
+      <c r="AS62" s="1"/>
+      <c r="AT62" s="1"/>
+      <c r="AU62" s="1"/>
+      <c r="AV62" s="1"/>
+      <c r="AW62" s="1"/>
+      <c r="AX62" s="1"/>
+      <c r="AY62" s="1"/>
+      <c r="AZ62" s="1"/>
+      <c r="BA62" s="1"/>
+      <c r="BB62" s="1"/>
+      <c r="BC62" s="1"/>
+      <c r="BD62" s="1"/>
+      <c r="BE62" s="1"/>
+      <c r="BF62" s="1"/>
+      <c r="BG62" s="1"/>
+      <c r="BH62" s="1"/>
+      <c r="BI62" s="1"/>
+      <c r="BJ62" s="1"/>
+      <c r="BK62" s="1"/>
+      <c r="BL62" s="1"/>
+      <c r="BM62" s="1"/>
+      <c r="BN62" s="1"/>
+      <c r="BO62" s="1"/>
+      <c r="BP62" s="1"/>
+      <c r="BQ62" s="1"/>
+      <c r="BR62" s="1"/>
+      <c r="BS62" s="1"/>
+      <c r="BT62" s="1"/>
+      <c r="BU62" s="1"/>
+      <c r="BV62" s="1"/>
+      <c r="BW62" s="1"/>
+      <c r="BX62" s="1"/>
+      <c r="BY62" s="1"/>
+      <c r="BZ62" s="1"/>
+      <c r="CA62" s="1"/>
+      <c r="CB62" s="1"/>
+      <c r="CC62" s="1"/>
+      <c r="CD62" s="1"/>
+      <c r="CE62" s="1"/>
+      <c r="CF62" s="1"/>
+      <c r="CG62" s="1"/>
+      <c r="CH62" s="1"/>
+      <c r="CI62" s="1"/>
+      <c r="CJ62" s="1"/>
+      <c r="CK62" s="1"/>
+      <c r="CL62" s="1"/>
+      <c r="CM62" s="1"/>
+      <c r="CN62" s="1"/>
+      <c r="CO62" s="1"/>
+      <c r="CP62" s="1"/>
+      <c r="CQ62" s="1"/>
+      <c r="CR62" s="1"/>
+      <c r="CS62" s="1"/>
+      <c r="CT62" s="1"/>
+      <c r="CU62" s="1"/>
+      <c r="CV62" s="1"/>
+      <c r="CW62" s="1"/>
+      <c r="CX62" s="1"/>
+      <c r="CY62" s="1"/>
+      <c r="CZ62" s="1"/>
+      <c r="DA62" s="1"/>
+      <c r="DB62" s="1"/>
+      <c r="DC62" s="1"/>
+      <c r="DD62" s="1"/>
+      <c r="DE62" s="1"/>
+      <c r="DF62" s="1"/>
+      <c r="DG62" s="1"/>
+      <c r="DH62" s="1"/>
+      <c r="DI62" s="1"/>
+      <c r="DJ62" s="1"/>
+      <c r="DK62" s="1"/>
+      <c r="DL62" s="1"/>
+      <c r="DM62" s="1"/>
+      <c r="DN62" s="1"/>
+      <c r="DO62" s="1"/>
+      <c r="DP62" s="1"/>
+      <c r="DQ62" s="1"/>
+      <c r="DR62" s="1"/>
+      <c r="DS62" s="1"/>
+      <c r="DT62" s="1"/>
+      <c r="DU62" s="1"/>
+      <c r="DV62" s="1"/>
+      <c r="DW62" s="1"/>
+      <c r="DX62" s="1"/>
+      <c r="DY62" s="1"/>
+      <c r="DZ62" s="1"/>
+      <c r="EA62" s="1"/>
+      <c r="EB62" s="1"/>
+      <c r="EC62" s="1"/>
+      <c r="ED62" s="1"/>
+      <c r="EE62" s="1"/>
+      <c r="EF62" s="1"/>
+      <c r="EG62" s="1"/>
+      <c r="EH62" s="1"/>
+      <c r="EI62" s="1"/>
+      <c r="EJ62" s="1"/>
+      <c r="EK62" s="1"/>
+      <c r="EL62" s="1"/>
+      <c r="EM62" s="1"/>
+      <c r="EN62" s="1"/>
+      <c r="EO62" s="1"/>
+      <c r="EP62" s="1"/>
+      <c r="EQ62" s="1"/>
+      <c r="ER62" s="1"/>
+      <c r="ES62" s="1"/>
+      <c r="ET62" s="1"/>
+      <c r="EU62" s="1"/>
+      <c r="EV62" s="1"/>
+      <c r="EW62" s="1"/>
+      <c r="EX62" s="1"/>
+      <c r="EY62" s="1"/>
+      <c r="EZ62" s="1"/>
+      <c r="FA62" s="1"/>
+      <c r="FB62" s="1"/>
+      <c r="FC62" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD62" s="1"/>
+      <c r="FE62" s="1"/>
+      <c r="FF62" s="1"/>
+      <c r="FG62" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="FH62" s="1"/>
+      <c r="FI62" s="1"/>
+      <c r="FJ62" s="1"/>
+      <c r="FK62" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL62" s="1"/>
+      <c r="FM62" s="1"/>
+      <c r="FN62" s="1"/>
+      <c r="FO62" s="1"/>
+      <c r="FP62" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="FQ62" s="1"/>
+      <c r="FR62" s="1"/>
+      <c r="FS62" s="1">
+        <v>-22.9295902170612</v>
+      </c>
+      <c r="FT62" s="1">
+        <v>-45.979329275508498</v>
+      </c>
+      <c r="FU62" s="1"/>
+      <c r="FV62" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW62" s="1"/>
+      <c r="FX62" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY62" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ62" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="GA62" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="GB62" s="1"/>
+      <c r="GC62" s="1"/>
+      <c r="GD62" s="1"/>
+      <c r="GE62" s="1"/>
+      <c r="GF62" s="1"/>
+      <c r="GG62" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="GH62" s="1"/>
+      <c r="GI62" s="1"/>
+      <c r="GJ62" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK62" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL62" s="1"/>
+      <c r="GM62" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN62" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO62" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="63" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G63" s="1">
+        <v>46129</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J63" s="1">
+        <v>-22.923100000000002</v>
+      </c>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1">
+        <v>-45.976080000000003</v>
+      </c>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="X63" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1">
+        <v>3000</v>
+      </c>
+      <c r="AB63" s="1">
+        <v>-22.922883299999999</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>-45.976044999999999</v>
+      </c>
+      <c r="AD63" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE63" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF63" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AG63" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH63" s="1">
+        <v>2018</v>
+      </c>
+      <c r="AI63" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ63" s="1"/>
+      <c r="AK63" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL63" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN63" s="1"/>
+      <c r="AO63" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP63" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AQ63" s="1"/>
+      <c r="AR63" s="1"/>
+      <c r="AS63" s="1"/>
+      <c r="AT63" s="1"/>
+      <c r="AU63" s="1"/>
+      <c r="AV63" s="1"/>
+      <c r="AW63" s="1"/>
+      <c r="AX63" s="1"/>
+      <c r="AY63" s="1"/>
+      <c r="AZ63" s="1"/>
+      <c r="BA63" s="1"/>
+      <c r="BB63" s="1"/>
+      <c r="BC63" s="1"/>
+      <c r="BD63" s="1"/>
+      <c r="BE63" s="1"/>
+      <c r="BF63" s="1"/>
+      <c r="BG63" s="1"/>
+      <c r="BH63" s="1"/>
+      <c r="BI63" s="1"/>
+      <c r="BJ63" s="1"/>
+      <c r="BK63" s="1"/>
+      <c r="BL63" s="1"/>
+      <c r="BM63" s="1"/>
+      <c r="BN63" s="1"/>
+      <c r="BO63" s="1"/>
+      <c r="BP63" s="1"/>
+      <c r="BQ63" s="1"/>
+      <c r="BR63" s="1"/>
+      <c r="BS63" s="1"/>
+      <c r="BT63" s="1"/>
+      <c r="BU63" s="1"/>
+      <c r="BV63" s="1"/>
+      <c r="BW63" s="1"/>
+      <c r="BX63" s="1"/>
+      <c r="BY63" s="1"/>
+      <c r="BZ63" s="1"/>
+      <c r="CA63" s="1"/>
+      <c r="CB63" s="1"/>
+      <c r="CC63" s="1"/>
+      <c r="CD63" s="1"/>
+      <c r="CE63" s="1"/>
+      <c r="CF63" s="1"/>
+      <c r="CG63" s="1"/>
+      <c r="CH63" s="1"/>
+      <c r="CI63" s="1"/>
+      <c r="CJ63" s="1"/>
+      <c r="CK63" s="1"/>
+      <c r="CL63" s="1"/>
+      <c r="CM63" s="1"/>
+      <c r="CN63" s="1"/>
+      <c r="CO63" s="1"/>
+      <c r="CP63" s="1"/>
+      <c r="CQ63" s="1"/>
+      <c r="CR63" s="1"/>
+      <c r="CS63" s="1"/>
+      <c r="CT63" s="1"/>
+      <c r="CU63" s="1"/>
+      <c r="CV63" s="1"/>
+      <c r="CW63" s="1"/>
+      <c r="CX63" s="1"/>
+      <c r="CY63" s="1"/>
+      <c r="CZ63" s="1"/>
+      <c r="DA63" s="1"/>
+      <c r="DB63" s="1"/>
+      <c r="DC63" s="1"/>
+      <c r="DD63" s="1"/>
+      <c r="DE63" s="1"/>
+      <c r="DF63" s="1"/>
+      <c r="DG63" s="1"/>
+      <c r="DH63" s="1"/>
+      <c r="DI63" s="1"/>
+      <c r="DJ63" s="1"/>
+      <c r="DK63" s="1"/>
+      <c r="DL63" s="1"/>
+      <c r="DM63" s="1"/>
+      <c r="DN63" s="1"/>
+      <c r="DO63" s="1"/>
+      <c r="DP63" s="1"/>
+      <c r="DQ63" s="1"/>
+      <c r="DR63" s="1"/>
+      <c r="DS63" s="1"/>
+      <c r="DT63" s="1"/>
+      <c r="DU63" s="1"/>
+      <c r="DV63" s="1"/>
+      <c r="DW63" s="1"/>
+      <c r="DX63" s="1"/>
+      <c r="DY63" s="1"/>
+      <c r="DZ63" s="1"/>
+      <c r="EA63" s="1"/>
+      <c r="EB63" s="1"/>
+      <c r="EC63" s="1"/>
+      <c r="ED63" s="1"/>
+      <c r="EE63" s="1"/>
+      <c r="EF63" s="1"/>
+      <c r="EG63" s="1"/>
+      <c r="EH63" s="1"/>
+      <c r="EI63" s="1"/>
+      <c r="EJ63" s="1"/>
+      <c r="EK63" s="1"/>
+      <c r="EL63" s="1"/>
+      <c r="EM63" s="1"/>
+      <c r="EN63" s="1"/>
+      <c r="EO63" s="1"/>
+      <c r="EP63" s="1"/>
+      <c r="EQ63" s="1"/>
+      <c r="ER63" s="1"/>
+      <c r="ES63" s="1"/>
+      <c r="ET63" s="1"/>
+      <c r="EU63" s="1"/>
+      <c r="EV63" s="1"/>
+      <c r="EW63" s="1"/>
+      <c r="EX63" s="1"/>
+      <c r="EY63" s="1"/>
+      <c r="EZ63" s="1"/>
+      <c r="FA63" s="1"/>
+      <c r="FB63" s="1"/>
+      <c r="FC63" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD63" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="FE63" s="1"/>
+      <c r="FF63" s="1"/>
+      <c r="FG63" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="FH63" s="1"/>
+      <c r="FI63" s="1"/>
+      <c r="FJ63" s="1"/>
+      <c r="FK63" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL63" s="1"/>
+      <c r="FM63" s="1"/>
+      <c r="FN63" s="1"/>
+      <c r="FO63" s="1"/>
+      <c r="FP63" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="FQ63" s="1"/>
+      <c r="FR63" s="1"/>
+      <c r="FS63" s="1">
+        <v>-22.946669439700699</v>
+      </c>
+      <c r="FT63" s="1">
+        <v>-45.960586862013898</v>
+      </c>
+      <c r="FU63" s="1"/>
+      <c r="FV63" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW63" s="1"/>
+      <c r="FX63" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY63" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ63" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="GA63" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="GB63" s="1"/>
+      <c r="GC63" s="1"/>
+      <c r="GD63" s="1"/>
+      <c r="GE63" s="1"/>
+      <c r="GF63" s="1"/>
+      <c r="GG63" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="GH63" s="1"/>
+      <c r="GI63" s="1"/>
+      <c r="GJ63" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL63" s="1"/>
+      <c r="GM63" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN63" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO63" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="1">
+        <v>46135</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J64" s="1">
+        <v>-22.928246999999999</v>
+      </c>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1">
+        <v>-45.969341999999997</v>
+      </c>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1">
+        <v>60</v>
+      </c>
+      <c r="AB64" s="1">
+        <v>-22.927888800000002</v>
+      </c>
+      <c r="AC64" s="1">
+        <v>-45.9686947</v>
+      </c>
+      <c r="AD64" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE64" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF64" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="AG64" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH64" s="1">
+        <v>1295</v>
+      </c>
+      <c r="AI64" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ64" s="1"/>
+      <c r="AK64" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AL64" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM64" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN64" s="1"/>
+      <c r="AO64" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP64" s="1"/>
+      <c r="AQ64" s="1">
+        <v>-22.9279546</v>
+      </c>
+      <c r="AR64" s="1">
+        <v>-45.9687488</v>
+      </c>
+      <c r="AS64" s="1"/>
+      <c r="AT64" s="1"/>
+      <c r="AU64" s="1"/>
+      <c r="AV64" s="1"/>
+      <c r="AW64" s="1"/>
+      <c r="AX64" s="1"/>
+      <c r="AY64" s="1"/>
+      <c r="AZ64" s="1"/>
+      <c r="BA64" s="1"/>
+      <c r="BB64" s="1"/>
+      <c r="BC64" s="1"/>
+      <c r="BD64" s="1"/>
+      <c r="BE64" s="1"/>
+      <c r="BF64" s="1"/>
+      <c r="BG64" s="1"/>
+      <c r="BH64" s="1"/>
+      <c r="BI64" s="1"/>
+      <c r="BJ64" s="1"/>
+      <c r="BK64" s="1"/>
+      <c r="BL64" s="1"/>
+      <c r="BM64" s="1"/>
+      <c r="BN64" s="1"/>
+      <c r="BO64" s="1"/>
+      <c r="BP64" s="1"/>
+      <c r="BQ64" s="1"/>
+      <c r="BR64" s="1"/>
+      <c r="BS64" s="1"/>
+      <c r="BT64" s="1"/>
+      <c r="BU64" s="1"/>
+      <c r="BV64" s="1"/>
+      <c r="BW64" s="1"/>
+      <c r="BX64" s="1"/>
+      <c r="BY64" s="1"/>
+      <c r="BZ64" s="1"/>
+      <c r="CA64" s="1"/>
+      <c r="CB64" s="1"/>
+      <c r="CC64" s="1"/>
+      <c r="CD64" s="1"/>
+      <c r="CE64" s="1"/>
+      <c r="CF64" s="1"/>
+      <c r="CG64" s="1"/>
+      <c r="CH64" s="1"/>
+      <c r="CI64" s="1"/>
+      <c r="CJ64" s="1"/>
+      <c r="CK64" s="1"/>
+      <c r="CL64" s="1"/>
+      <c r="CM64" s="1"/>
+      <c r="CN64" s="1"/>
+      <c r="CO64" s="1"/>
+      <c r="CP64" s="1"/>
+      <c r="CQ64" s="1"/>
+      <c r="CR64" s="1"/>
+      <c r="CS64" s="1"/>
+      <c r="CT64" s="1"/>
+      <c r="CU64" s="1"/>
+      <c r="CV64" s="1"/>
+      <c r="CW64" s="1"/>
+      <c r="CX64" s="1"/>
+      <c r="CY64" s="1"/>
+      <c r="CZ64" s="1"/>
+      <c r="DA64" s="1"/>
+      <c r="DB64" s="1"/>
+      <c r="DC64" s="1"/>
+      <c r="DD64" s="1"/>
+      <c r="DE64" s="1"/>
+      <c r="DF64" s="1"/>
+      <c r="DG64" s="1"/>
+      <c r="DH64" s="1"/>
+      <c r="DI64" s="1"/>
+      <c r="DJ64" s="1"/>
+      <c r="DK64" s="1"/>
+      <c r="DL64" s="1"/>
+      <c r="DM64" s="1"/>
+      <c r="DN64" s="1"/>
+      <c r="DO64" s="1"/>
+      <c r="DP64" s="1"/>
+      <c r="DQ64" s="1"/>
+      <c r="DR64" s="1"/>
+      <c r="DS64" s="1"/>
+      <c r="DT64" s="1"/>
+      <c r="DU64" s="1"/>
+      <c r="DV64" s="1"/>
+      <c r="DW64" s="1"/>
+      <c r="DX64" s="1"/>
+      <c r="DY64" s="1"/>
+      <c r="DZ64" s="1"/>
+      <c r="EA64" s="1"/>
+      <c r="EB64" s="1"/>
+      <c r="EC64" s="1"/>
+      <c r="ED64" s="1"/>
+      <c r="EE64" s="1"/>
+      <c r="EF64" s="1"/>
+      <c r="EG64" s="1"/>
+      <c r="EH64" s="1"/>
+      <c r="EI64" s="1"/>
+      <c r="EJ64" s="1"/>
+      <c r="EK64" s="1"/>
+      <c r="EL64" s="1"/>
+      <c r="EM64" s="1"/>
+      <c r="EN64" s="1"/>
+      <c r="EO64" s="1"/>
+      <c r="EP64" s="1"/>
+      <c r="EQ64" s="1"/>
+      <c r="ER64" s="1"/>
+      <c r="ES64" s="1"/>
+      <c r="ET64" s="1"/>
+      <c r="EU64" s="1"/>
+      <c r="EV64" s="1"/>
+      <c r="EW64" s="1"/>
+      <c r="EX64" s="1"/>
+      <c r="EY64" s="1"/>
+      <c r="EZ64" s="1"/>
+      <c r="FA64" s="1"/>
+      <c r="FB64" s="1"/>
+      <c r="FC64" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="FD64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="FE64" s="1"/>
+      <c r="FF64" s="1"/>
+      <c r="FG64" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="FH64" s="1"/>
+      <c r="FI64" s="1"/>
+      <c r="FJ64" s="1"/>
+      <c r="FK64" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="FL64" s="1"/>
+      <c r="FM64" s="1"/>
+      <c r="FN64" s="1"/>
+      <c r="FO64" s="1"/>
+      <c r="FP64" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="FQ64" s="1"/>
+      <c r="FR64" s="1"/>
+      <c r="FS64" s="1">
+        <v>-22.944800219270501</v>
+      </c>
+      <c r="FT64" s="1">
+        <v>-45.984118546672697</v>
+      </c>
+      <c r="FU64" s="1"/>
+      <c r="FV64" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="FW64" s="1"/>
+      <c r="FX64" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="FY64" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FZ64" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="GA64" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="GB64" s="1"/>
+      <c r="GC64" s="1"/>
+      <c r="GD64" s="1"/>
+      <c r="GE64" s="1"/>
+      <c r="GF64" s="1"/>
+      <c r="GG64" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="GH64" s="1"/>
+      <c r="GI64" s="1"/>
+      <c r="GJ64" s="1">
+        <v>1</v>
+      </c>
+      <c r="GK64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="GL64" s="1"/>
+      <c r="GM64" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="GN64" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="GO64" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="171:171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="FO71" s="10"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -15857,7 +21325,50 @@
     <hyperlink ref="AP45" r:id="rId103" xr:uid="{9878E0D0-87EA-495F-8138-5CCCBDFFDC21}"/>
     <hyperlink ref="A46" r:id="rId104" xr:uid="{3DDE3DBB-D070-440A-AEB5-5DDCA47C4425}"/>
     <hyperlink ref="AL46" r:id="rId105" xr:uid="{138FF092-2C26-47B0-93C9-596C503FF426}"/>
+    <hyperlink ref="A47" r:id="rId106" xr:uid="{EBC490F4-5526-4C57-BB67-2EA8D88F9C0D}"/>
+    <hyperlink ref="AL47" r:id="rId107" xr:uid="{82EA4A10-A223-417B-AFC8-CB9FBFD3112A}"/>
+    <hyperlink ref="AP47" r:id="rId108" xr:uid="{36C3F6DF-C3ED-436E-B203-CA98A953299F}"/>
+    <hyperlink ref="A48" r:id="rId109" xr:uid="{7BB35DB4-1B8C-4139-8B59-74D9F351096D}"/>
+    <hyperlink ref="AL48" r:id="rId110" xr:uid="{709EC5B1-5338-4F1D-8F97-FE2EB444761B}"/>
+    <hyperlink ref="AP48" r:id="rId111" xr:uid="{7E04A026-8C0D-4E42-BE79-5675F837F48A}"/>
+    <hyperlink ref="A49" r:id="rId112" xr:uid="{52391D5D-1623-4B84-A833-C2D78282D32B}"/>
+    <hyperlink ref="AL49" r:id="rId113" xr:uid="{2FAF3B03-14CE-46C6-9EA9-C5070D8242B7}"/>
+    <hyperlink ref="AP49" r:id="rId114" xr:uid="{77CC1664-9AC1-480B-A964-844D184AA84B}"/>
+    <hyperlink ref="A50" r:id="rId115" xr:uid="{AFB70D59-47B7-4A8C-949F-4FEEAE10C4B1}"/>
+    <hyperlink ref="A51" r:id="rId116" xr:uid="{B496352A-D43E-4317-A1AF-A5F6949D0843}"/>
+    <hyperlink ref="AL51" r:id="rId117" xr:uid="{C4A98AAB-3D7C-4E68-BC27-3A24FAD20D85}"/>
+    <hyperlink ref="A52" r:id="rId118" xr:uid="{2CEA866E-D7B3-44EF-916B-9605A2620F6A}"/>
+    <hyperlink ref="AL52" r:id="rId119" display="https://s3.deepessoas.com/registros/USCR/050ecf5e-45c3-4e65-8a31-da15f31fca3d/1976ecb5-366f-45e2-9f26-2c68e3bbaa9f/2026-04-16/026fe8ce-a251-49b2-8d49-ea4cbab30455.jpeg_x000a_https://s3.deepessoas.com/registros/USCR/050ecf5e-45c3-4e65-8a31-da15f31fca3d/1976ecb5-366f-45e2-9f26-2c68e3bbaa9f/2026-04-16/21c662e5-0f48-4316-b7cf-4adba3fccb66.jpeg" xr:uid="{6F926FE4-1420-47FD-8E8A-AAEDCC7A3588}"/>
+    <hyperlink ref="A53" r:id="rId120" xr:uid="{1EC355C4-CC8F-4B29-A995-4867FAF8DB17}"/>
+    <hyperlink ref="AL53" r:id="rId121" xr:uid="{42AF4490-F71E-457C-A65E-9DD6BAA08704}"/>
+    <hyperlink ref="A54" r:id="rId122" xr:uid="{95C32615-929A-424B-91BD-877B7B26B7DC}"/>
+    <hyperlink ref="AL54" r:id="rId123" xr:uid="{6C3C1608-1FAF-4BB5-8AF9-548DF71C4F2D}"/>
+    <hyperlink ref="AP54" r:id="rId124" xr:uid="{6AFB905A-12F1-48F7-BAF6-5FF26169B3FF}"/>
+    <hyperlink ref="A55" r:id="rId125" xr:uid="{F3C914DF-EFB1-48BA-AFA0-76716CD18307}"/>
+    <hyperlink ref="AL55" r:id="rId126" xr:uid="{FB58DE1C-450E-42AD-BE29-B5DFADDC8A0C}"/>
+    <hyperlink ref="A56" r:id="rId127" xr:uid="{17AA7518-08DE-46E8-8B02-52F542906237}"/>
+    <hyperlink ref="AL56" r:id="rId128" xr:uid="{D8DD92F5-4C18-4077-9C55-F25B19673188}"/>
+    <hyperlink ref="AP56" r:id="rId129" xr:uid="{0B4BF1C2-24DB-49DD-8041-29FBE09D9B1D}"/>
+    <hyperlink ref="A57" r:id="rId130" xr:uid="{DA0AD591-1B09-44B1-A7EE-248F9E4BFA36}"/>
+    <hyperlink ref="AL57" r:id="rId131" xr:uid="{14514075-94B9-46EE-ABC9-0E7D74EEC88E}"/>
+    <hyperlink ref="AP57" r:id="rId132" xr:uid="{D9808933-A440-45CA-983B-DB0AB6CE9595}"/>
+    <hyperlink ref="A58" r:id="rId133" xr:uid="{4D67037F-B0A2-4B9A-ACC2-61378E06A789}"/>
+    <hyperlink ref="AL58" r:id="rId134" xr:uid="{8AF830E4-AF2E-4251-98C3-112FCB6FE6A9}"/>
+    <hyperlink ref="AP58" r:id="rId135" xr:uid="{9AEA46ED-25C0-481D-9D5D-A265C03CF2F8}"/>
+    <hyperlink ref="A59" r:id="rId136" xr:uid="{BCDEF1AF-E80C-4388-833C-9B755979A291}"/>
+    <hyperlink ref="A60" r:id="rId137" xr:uid="{813E6260-514C-438C-9507-99598AA26F3F}"/>
+    <hyperlink ref="AL60" r:id="rId138" xr:uid="{15594C13-CA64-4CD4-8E91-3A8A7FE2DF6B}"/>
+    <hyperlink ref="A61" r:id="rId139" xr:uid="{DE0C0FC6-4AE3-4D68-82B4-47E28EFBB45A}"/>
+    <hyperlink ref="AL61" r:id="rId140" display="https://s3.deepessoas.com/registros/USCR/050ecf5e-45c3-4e65-8a31-da15f31fca3d/1976ecb5-366f-45e2-9f26-2c68e3bbaa9f/2026-04-16/026fe8ce-a251-49b2-8d49-ea4cbab30455.jpeg_x000a_https://s3.deepessoas.com/registros/USCR/050ecf5e-45c3-4e65-8a31-da15f31fca3d/1976ecb5-366f-45e2-9f26-2c68e3bbaa9f/2026-04-16/21c662e5-0f48-4316-b7cf-4adba3fccb66.jpeg" xr:uid="{7A8E89CF-F455-46B5-BE1D-D063B4DEFC7A}"/>
+    <hyperlink ref="A62" r:id="rId141" xr:uid="{E1E6D10C-F264-4F45-BF69-887806834AAF}"/>
+    <hyperlink ref="AL62" r:id="rId142" xr:uid="{4AB0CC0A-29D9-41C9-BE80-44D6D5729E4F}"/>
+    <hyperlink ref="A63" r:id="rId143" xr:uid="{84BFD235-51D6-46A2-915D-D3B3FA41DE05}"/>
+    <hyperlink ref="AL63" r:id="rId144" xr:uid="{9121575F-1821-4439-B1B7-FA585C924565}"/>
+    <hyperlink ref="AP63" r:id="rId145" xr:uid="{0D3B9885-B03C-4A97-B5FE-D43E448C0C6B}"/>
+    <hyperlink ref="A64" r:id="rId146" xr:uid="{57A990B6-07A4-489F-83F6-273975F1F2F6}"/>
+    <hyperlink ref="AL64" r:id="rId147" xr:uid="{DDBF224A-480A-4D2E-A553-0F59B3DDEAB4}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId148"/>
 </worksheet>
 </file>